--- a/app/public/発注フォーム.xlsx
+++ b/app/public/発注フォーム.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\masuda-vinyl-ops\app\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D8D1E0B-59BB-4077-9570-5AEDA819653A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D620FF6-1B75-4B44-B918-9201A746CEBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-41055" yWindow="-16380" windowWidth="21600" windowHeight="15585" xr2:uid="{811621DE-664E-4521-9512-F04E9755C0E8}"/>
+    <workbookView xWindow="2775" yWindow="1410" windowWidth="21600" windowHeight="15870" xr2:uid="{811621DE-664E-4521-9512-F04E9755C0E8}"/>
   </bookViews>
   <sheets>
     <sheet name="Duc Phong" sheetId="170" r:id="rId1"/>
@@ -515,8 +515,8 @@
     <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="177" formatCode="##&quot;邸&quot;"/>
     <numFmt numFmtId="178" formatCode="d/m"/>
-    <numFmt numFmtId="180" formatCode="0,000\ &quot;VND&quot;"/>
-    <numFmt numFmtId="181" formatCode="d/m/yyyy"/>
+    <numFmt numFmtId="179" formatCode="0,000\ &quot;VND&quot;"/>
+    <numFmt numFmtId="180" formatCode="d/m/yyyy"/>
   </numFmts>
   <fonts count="38">
     <font>
@@ -1134,7 +1134,7 @@
     <xf numFmtId="176" fontId="6" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="6" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="6" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1156,7 +1156,7 @@
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1170,6 +1170,84 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="18" fillId="0" borderId="20" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="18" fillId="0" borderId="21" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="15" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="15" fillId="0" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="18" fillId="0" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="18" fillId="0" borderId="15" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="15" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="15" fillId="0" borderId="16" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1192,93 +1270,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="180" fontId="15" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="15" fillId="0" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="18" fillId="0" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="18" fillId="0" borderId="15" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="15" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="15" fillId="0" borderId="16" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="18" fillId="0" borderId="20" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="18" fillId="0" borderId="21" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1290,6 +1281,15 @@
     </xf>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2465,16 +2465,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:10" ht="54" customHeight="1">
-      <c r="C1" s="37" t="s">
+      <c r="C1" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
-      <c r="J1" s="38"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
+      <c r="H1" s="64"/>
+      <c r="I1" s="64"/>
+      <c r="J1" s="64"/>
     </row>
     <row r="2" spans="2:10" ht="21.75" customHeight="1">
       <c r="C2" s="36"/>
@@ -2484,7 +2484,7 @@
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
-      <c r="J2" s="73" t="s">
+      <c r="J2" s="38" t="s">
         <v>23</v>
       </c>
     </row>
@@ -2496,7 +2496,7 @@
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
-      <c r="J3" s="72" t="s">
+      <c r="J3" s="37" t="s">
         <v>24</v>
       </c>
     </row>
@@ -2542,9 +2542,9 @@
       <c r="J6" s="11"/>
     </row>
     <row r="7" spans="2:10" ht="18.75" customHeight="1">
-      <c r="B7" s="39"/>
-      <c r="C7" s="39"/>
-      <c r="D7" s="39"/>
+      <c r="B7" s="65"/>
+      <c r="C7" s="65"/>
+      <c r="D7" s="65"/>
       <c r="E7" s="2"/>
       <c r="F7" s="5"/>
       <c r="G7" s="5"/>
@@ -2562,26 +2562,26 @@
       <c r="I8" s="6"/>
     </row>
     <row r="9" spans="2:10" s="8" customFormat="1" ht="18" customHeight="1">
-      <c r="B9" s="40" t="s">
+      <c r="B9" s="66" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="40"/>
-      <c r="D9" s="40"/>
-      <c r="E9" s="40"/>
-      <c r="F9" s="40"/>
-      <c r="G9" s="40"/>
+      <c r="C9" s="66"/>
+      <c r="D9" s="66"/>
+      <c r="E9" s="66"/>
+      <c r="F9" s="66"/>
+      <c r="G9" s="66"/>
       <c r="H9" s="17"/>
       <c r="I9" s="17"/>
     </row>
     <row r="10" spans="2:10" ht="18" customHeight="1">
-      <c r="B10" s="41" t="s">
+      <c r="B10" s="67" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="41"/>
-      <c r="D10" s="41"/>
-      <c r="E10" s="41"/>
-      <c r="F10" s="41"/>
-      <c r="G10" s="41"/>
+      <c r="C10" s="67"/>
+      <c r="D10" s="67"/>
+      <c r="E10" s="67"/>
+      <c r="F10" s="67"/>
+      <c r="G10" s="67"/>
     </row>
     <row r="11" spans="2:10" ht="18" customHeight="1" thickBot="1">
       <c r="D11" s="1"/>
@@ -2593,10 +2593,10 @@
       <c r="B12" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="C12" s="42" t="s">
+      <c r="C12" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="D12" s="43"/>
+      <c r="D12" s="69"/>
       <c r="E12" s="13" t="s">
         <v>6</v>
       </c>
@@ -2609,19 +2609,19 @@
       <c r="H12" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="I12" s="42" t="s">
+      <c r="I12" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="J12" s="44"/>
+      <c r="J12" s="70"/>
     </row>
     <row r="13" spans="2:10" ht="16.5">
       <c r="B13" s="16">
         <v>1</v>
       </c>
-      <c r="C13" s="45" t="s">
+      <c r="C13" s="49" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="45"/>
+      <c r="D13" s="49"/>
       <c r="E13" s="9" t="s">
         <v>13</v>
       </c>
@@ -2632,168 +2632,168 @@
         <v>6600</v>
       </c>
       <c r="H13" s="19"/>
-      <c r="I13" s="46">
+      <c r="I13" s="53">
         <f>IF(NOT(G13*F13=0), G13*F13, "")</f>
         <v>3300000</v>
       </c>
-      <c r="J13" s="47"/>
+      <c r="J13" s="54"/>
     </row>
     <row r="14" spans="2:10" ht="21" customHeight="1">
       <c r="B14" s="16">
         <f>B13+1</f>
         <v>2</v>
       </c>
-      <c r="C14" s="45"/>
-      <c r="D14" s="45"/>
+      <c r="C14" s="49"/>
+      <c r="D14" s="49"/>
       <c r="E14" s="9"/>
       <c r="F14" s="10"/>
       <c r="G14" s="23"/>
       <c r="H14" s="19"/>
-      <c r="I14" s="46" t="str">
+      <c r="I14" s="53" t="str">
         <f>IF(NOT(G14*F14=0), G14*F14, "")</f>
         <v/>
       </c>
-      <c r="J14" s="47"/>
+      <c r="J14" s="54"/>
     </row>
     <row r="15" spans="2:10" ht="20.100000000000001" customHeight="1">
       <c r="B15" s="15">
         <f>B14+1</f>
         <v>3</v>
       </c>
-      <c r="C15" s="48"/>
-      <c r="D15" s="48"/>
+      <c r="C15" s="52"/>
+      <c r="D15" s="52"/>
       <c r="E15" s="9"/>
       <c r="F15" s="10"/>
       <c r="G15" s="22"/>
       <c r="H15" s="19"/>
-      <c r="I15" s="46" t="str">
+      <c r="I15" s="53" t="str">
         <f t="shared" ref="I15:I19" si="0">IF(NOT(G15*F15=0), G15*F15, "")</f>
         <v/>
       </c>
-      <c r="J15" s="47"/>
+      <c r="J15" s="54"/>
     </row>
     <row r="16" spans="2:10" ht="20.100000000000001" customHeight="1">
       <c r="B16" s="15">
         <f>B15+1</f>
         <v>4</v>
       </c>
-      <c r="C16" s="48"/>
-      <c r="D16" s="48"/>
+      <c r="C16" s="52"/>
+      <c r="D16" s="52"/>
       <c r="E16" s="9"/>
       <c r="F16" s="10"/>
       <c r="G16" s="22"/>
       <c r="H16" s="19"/>
-      <c r="I16" s="46" t="str">
+      <c r="I16" s="53" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="J16" s="47"/>
+      <c r="J16" s="54"/>
     </row>
     <row r="17" spans="2:10" ht="20.100000000000001" customHeight="1">
       <c r="B17" s="15">
         <f>B16+1</f>
         <v>5</v>
       </c>
-      <c r="C17" s="48"/>
-      <c r="D17" s="48"/>
+      <c r="C17" s="52"/>
+      <c r="D17" s="52"/>
       <c r="E17" s="9"/>
       <c r="F17" s="10"/>
       <c r="G17" s="22"/>
       <c r="H17" s="19"/>
-      <c r="I17" s="46" t="str">
+      <c r="I17" s="53" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="J17" s="47"/>
+      <c r="J17" s="54"/>
     </row>
     <row r="18" spans="2:10" ht="20.100000000000001" customHeight="1">
       <c r="B18" s="15">
         <f>B17+1</f>
         <v>6</v>
       </c>
-      <c r="C18" s="48"/>
-      <c r="D18" s="48"/>
+      <c r="C18" s="52"/>
+      <c r="D18" s="52"/>
       <c r="E18" s="9"/>
       <c r="F18" s="10"/>
       <c r="G18" s="22"/>
       <c r="H18" s="19"/>
-      <c r="I18" s="46" t="str">
+      <c r="I18" s="53" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="J18" s="47"/>
+      <c r="J18" s="54"/>
     </row>
     <row r="19" spans="2:10" ht="20.100000000000001" customHeight="1">
       <c r="B19" s="15">
         <v>7</v>
       </c>
-      <c r="C19" s="48"/>
-      <c r="D19" s="48"/>
+      <c r="C19" s="52"/>
+      <c r="D19" s="52"/>
       <c r="E19" s="9"/>
       <c r="F19" s="10"/>
       <c r="G19" s="22"/>
       <c r="H19" s="19"/>
-      <c r="I19" s="46" t="str">
+      <c r="I19" s="53" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="J19" s="47"/>
+      <c r="J19" s="54"/>
     </row>
     <row r="20" spans="2:10" ht="30" customHeight="1">
-      <c r="B20" s="49" t="s">
+      <c r="B20" s="55" t="s">
         <v>9</v>
       </c>
-      <c r="C20" s="50"/>
-      <c r="D20" s="50"/>
-      <c r="E20" s="50"/>
-      <c r="F20" s="50"/>
-      <c r="G20" s="50"/>
-      <c r="H20" s="51"/>
-      <c r="I20" s="52">
+      <c r="C20" s="56"/>
+      <c r="D20" s="56"/>
+      <c r="E20" s="56"/>
+      <c r="F20" s="56"/>
+      <c r="G20" s="56"/>
+      <c r="H20" s="57"/>
+      <c r="I20" s="58">
         <f>SUM(I13:J19)</f>
         <v>3300000</v>
       </c>
-      <c r="J20" s="53"/>
+      <c r="J20" s="59"/>
     </row>
     <row r="21" spans="2:10" ht="30" customHeight="1">
-      <c r="B21" s="54" t="s">
+      <c r="B21" s="60" t="s">
         <v>12</v>
       </c>
-      <c r="C21" s="50"/>
-      <c r="D21" s="50"/>
-      <c r="E21" s="50"/>
-      <c r="F21" s="50"/>
-      <c r="G21" s="50"/>
-      <c r="H21" s="51"/>
-      <c r="I21" s="55"/>
-      <c r="J21" s="56"/>
+      <c r="C21" s="56"/>
+      <c r="D21" s="56"/>
+      <c r="E21" s="56"/>
+      <c r="F21" s="56"/>
+      <c r="G21" s="56"/>
+      <c r="H21" s="57"/>
+      <c r="I21" s="61"/>
+      <c r="J21" s="62"/>
     </row>
     <row r="22" spans="2:10" ht="30" customHeight="1" thickBot="1">
-      <c r="B22" s="57" t="s">
+      <c r="B22" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="C22" s="58"/>
-      <c r="D22" s="58"/>
-      <c r="E22" s="58"/>
-      <c r="F22" s="58"/>
-      <c r="G22" s="58"/>
-      <c r="H22" s="59"/>
-      <c r="I22" s="60">
+      <c r="C22" s="42"/>
+      <c r="D22" s="42"/>
+      <c r="E22" s="42"/>
+      <c r="F22" s="42"/>
+      <c r="G22" s="42"/>
+      <c r="H22" s="43"/>
+      <c r="I22" s="44">
         <f>I20+I21</f>
         <v>3300000</v>
       </c>
-      <c r="J22" s="61"/>
+      <c r="J22" s="45"/>
     </row>
     <row r="23" spans="2:10" ht="44.25" customHeight="1" thickBot="1">
-      <c r="B23" s="62"/>
-      <c r="C23" s="63"/>
-      <c r="D23" s="63"/>
-      <c r="E23" s="63"/>
-      <c r="F23" s="63"/>
-      <c r="G23" s="63"/>
-      <c r="H23" s="63"/>
-      <c r="I23" s="63"/>
-      <c r="J23" s="64"/>
+      <c r="B23" s="75"/>
+      <c r="C23" s="76"/>
+      <c r="D23" s="76"/>
+      <c r="E23" s="76"/>
+      <c r="F23" s="76"/>
+      <c r="G23" s="76"/>
+      <c r="H23" s="76"/>
+      <c r="I23" s="76"/>
+      <c r="J23" s="77"/>
     </row>
     <row r="24" spans="2:10" ht="17.25" customHeight="1">
       <c r="D24" s="1"/>
@@ -2802,9 +2802,9 @@
       <c r="G24" s="1"/>
     </row>
     <row r="25" spans="2:10" ht="48" customHeight="1">
-      <c r="B25" s="65"/>
-      <c r="C25" s="65"/>
-      <c r="D25" s="65"/>
+      <c r="B25" s="46"/>
+      <c r="C25" s="46"/>
+      <c r="D25" s="46"/>
       <c r="E25" s="29"/>
       <c r="F25" s="32"/>
       <c r="G25" s="33" t="s">
@@ -2813,37 +2813,37 @@
       <c r="H25" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="I25" s="68" t="s">
+      <c r="I25" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="J25" s="68"/>
+      <c r="J25" s="50"/>
     </row>
     <row r="26" spans="2:10" ht="36.75" customHeight="1">
       <c r="B26" s="30"/>
-      <c r="C26" s="66"/>
-      <c r="D26" s="67"/>
+      <c r="C26" s="47"/>
+      <c r="D26" s="48"/>
       <c r="E26" s="30"/>
-      <c r="F26" s="66"/>
-      <c r="G26" s="45"/>
-      <c r="H26" s="45"/>
-      <c r="I26" s="69"/>
-      <c r="J26" s="69"/>
+      <c r="F26" s="47"/>
+      <c r="G26" s="49"/>
+      <c r="H26" s="49"/>
+      <c r="I26" s="51"/>
+      <c r="J26" s="51"/>
     </row>
     <row r="27" spans="2:10" ht="30" customHeight="1">
       <c r="B27" s="28"/>
-      <c r="C27" s="70"/>
-      <c r="D27" s="70"/>
+      <c r="C27" s="39"/>
+      <c r="D27" s="39"/>
       <c r="E27" s="27"/>
-      <c r="F27" s="66"/>
-      <c r="G27" s="45"/>
-      <c r="H27" s="45"/>
-      <c r="I27" s="69"/>
-      <c r="J27" s="69"/>
+      <c r="F27" s="47"/>
+      <c r="G27" s="49"/>
+      <c r="H27" s="49"/>
+      <c r="I27" s="51"/>
+      <c r="J27" s="51"/>
     </row>
     <row r="28" spans="2:10" ht="30" customHeight="1">
       <c r="B28" s="6"/>
-      <c r="C28" s="70"/>
-      <c r="D28" s="70"/>
+      <c r="C28" s="39"/>
+      <c r="D28" s="39"/>
       <c r="E28" s="27"/>
       <c r="F28" s="20"/>
       <c r="G28" s="20"/>
@@ -2853,8 +2853,8 @@
     </row>
     <row r="29" spans="2:10" ht="30" customHeight="1">
       <c r="B29" s="6"/>
-      <c r="C29" s="70"/>
-      <c r="D29" s="70"/>
+      <c r="C29" s="39"/>
+      <c r="D29" s="39"/>
       <c r="E29" s="27"/>
       <c r="F29" s="20"/>
       <c r="G29" s="20"/>
@@ -2864,8 +2864,8 @@
     </row>
     <row r="30" spans="2:10" ht="30" customHeight="1">
       <c r="B30" s="6"/>
-      <c r="C30" s="70"/>
-      <c r="D30" s="70"/>
+      <c r="C30" s="39"/>
+      <c r="D30" s="39"/>
       <c r="E30" s="27"/>
       <c r="F30" s="20"/>
       <c r="G30" s="20"/>
@@ -2875,8 +2875,8 @@
     </row>
     <row r="31" spans="2:10" ht="30" customHeight="1">
       <c r="B31" s="6"/>
-      <c r="C31" s="70"/>
-      <c r="D31" s="70"/>
+      <c r="C31" s="39"/>
+      <c r="D31" s="39"/>
       <c r="E31" s="27"/>
       <c r="F31" s="20"/>
       <c r="G31" s="20"/>
@@ -2886,8 +2886,8 @@
     </row>
     <row r="32" spans="2:10" ht="30" customHeight="1">
       <c r="B32" s="6"/>
-      <c r="C32" s="70"/>
-      <c r="D32" s="70"/>
+      <c r="C32" s="39"/>
+      <c r="D32" s="39"/>
       <c r="E32" s="27"/>
       <c r="F32" s="21"/>
       <c r="G32" s="21"/>
@@ -2897,8 +2897,8 @@
     </row>
     <row r="33" spans="2:10" ht="30" customHeight="1">
       <c r="B33" s="6"/>
-      <c r="C33" s="71"/>
-      <c r="D33" s="71"/>
+      <c r="C33" s="40"/>
+      <c r="D33" s="40"/>
       <c r="E33" s="28"/>
       <c r="F33" s="21"/>
       <c r="G33" s="21"/>
@@ -2908,8 +2908,8 @@
     </row>
     <row r="34" spans="2:10" ht="30" customHeight="1">
       <c r="B34" s="6"/>
-      <c r="C34" s="71"/>
-      <c r="D34" s="71"/>
+      <c r="C34" s="40"/>
+      <c r="D34" s="40"/>
       <c r="E34" s="28"/>
       <c r="F34" s="21"/>
       <c r="G34" s="21"/>
@@ -2919,8 +2919,8 @@
     </row>
     <row r="35" spans="2:10" ht="30" customHeight="1">
       <c r="B35" s="6"/>
-      <c r="C35" s="71"/>
-      <c r="D35" s="71"/>
+      <c r="C35" s="40"/>
+      <c r="D35" s="40"/>
       <c r="E35" s="28"/>
       <c r="F35" s="21"/>
       <c r="G35" s="21"/>
@@ -2944,15 +2944,30 @@
     <row r="49" ht="20.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="C1:J1"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B9:G9"/>
+    <mergeCell ref="B10:G10"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="B20:H20"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="B21:H21"/>
+    <mergeCell ref="I21:J21"/>
     <mergeCell ref="B22:H22"/>
     <mergeCell ref="I22:J22"/>
     <mergeCell ref="B23:J23"/>
@@ -2963,30 +2978,15 @@
     <mergeCell ref="F26:F27"/>
     <mergeCell ref="I25:J25"/>
     <mergeCell ref="I26:J27"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="B20:H20"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="B21:H21"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="C1:J1"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="B9:G9"/>
-    <mergeCell ref="B10:G10"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="C31:D31"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.12" right="0.16" top="0.22" bottom="0.12" header="0.3" footer="0.3"/>
@@ -3017,16 +3017,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:10" ht="54" customHeight="1">
-      <c r="C1" s="37" t="s">
+      <c r="C1" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
-      <c r="J1" s="38"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
+      <c r="H1" s="64"/>
+      <c r="I1" s="64"/>
+      <c r="J1" s="64"/>
     </row>
     <row r="2" spans="2:10" ht="21.75" customHeight="1">
       <c r="C2" s="36"/>
@@ -3036,7 +3036,7 @@
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
-      <c r="J2" s="73" t="s">
+      <c r="J2" s="38" t="s">
         <v>23</v>
       </c>
     </row>
@@ -3048,7 +3048,7 @@
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
-      <c r="J3" s="72" t="s">
+      <c r="J3" s="37" t="s">
         <v>24</v>
       </c>
     </row>
@@ -3094,9 +3094,9 @@
       <c r="J6" s="11"/>
     </row>
     <row r="7" spans="2:10" ht="18.75" customHeight="1">
-      <c r="B7" s="39"/>
-      <c r="C7" s="39"/>
-      <c r="D7" s="39"/>
+      <c r="B7" s="65"/>
+      <c r="C7" s="65"/>
+      <c r="D7" s="65"/>
       <c r="E7" s="2"/>
       <c r="F7" s="5"/>
       <c r="G7" s="5"/>
@@ -3114,26 +3114,26 @@
       <c r="I8" s="6"/>
     </row>
     <row r="9" spans="2:10" s="8" customFormat="1" ht="18" customHeight="1">
-      <c r="B9" s="40" t="s">
+      <c r="B9" s="66" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="40"/>
-      <c r="D9" s="40"/>
-      <c r="E9" s="40"/>
-      <c r="F9" s="40"/>
-      <c r="G9" s="40"/>
+      <c r="C9" s="66"/>
+      <c r="D9" s="66"/>
+      <c r="E9" s="66"/>
+      <c r="F9" s="66"/>
+      <c r="G9" s="66"/>
       <c r="H9" s="17"/>
       <c r="I9" s="17"/>
     </row>
     <row r="10" spans="2:10" ht="18" customHeight="1">
-      <c r="B10" s="41" t="s">
+      <c r="B10" s="67" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="41"/>
-      <c r="D10" s="41"/>
-      <c r="E10" s="41"/>
-      <c r="F10" s="41"/>
-      <c r="G10" s="41"/>
+      <c r="C10" s="67"/>
+      <c r="D10" s="67"/>
+      <c r="E10" s="67"/>
+      <c r="F10" s="67"/>
+      <c r="G10" s="67"/>
     </row>
     <row r="11" spans="2:10" ht="18" customHeight="1" thickBot="1">
       <c r="D11" s="1"/>
@@ -3145,10 +3145,10 @@
       <c r="B12" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="C12" s="42" t="s">
+      <c r="C12" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="D12" s="43"/>
+      <c r="D12" s="69"/>
       <c r="E12" s="13" t="s">
         <v>6</v>
       </c>
@@ -3161,19 +3161,19 @@
       <c r="H12" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="I12" s="42" t="s">
+      <c r="I12" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="J12" s="44"/>
+      <c r="J12" s="70"/>
     </row>
     <row r="13" spans="2:10" ht="16.5">
       <c r="B13" s="16">
         <v>1</v>
       </c>
-      <c r="C13" s="45" t="s">
+      <c r="C13" s="49" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="45"/>
+      <c r="D13" s="49"/>
       <c r="E13" s="9" t="s">
         <v>13</v>
       </c>
@@ -3184,243 +3184,243 @@
         <v>6600</v>
       </c>
       <c r="H13" s="19"/>
-      <c r="I13" s="46">
+      <c r="I13" s="53">
         <f>IF(NOT(G13*F13=0), G13*F13, "")</f>
         <v>3300000</v>
       </c>
-      <c r="J13" s="47"/>
+      <c r="J13" s="54"/>
     </row>
     <row r="14" spans="2:10" ht="21" customHeight="1">
       <c r="B14" s="16">
         <v>2</v>
       </c>
-      <c r="C14" s="45"/>
-      <c r="D14" s="45"/>
+      <c r="C14" s="49"/>
+      <c r="D14" s="49"/>
       <c r="E14" s="9"/>
       <c r="F14" s="10"/>
       <c r="G14" s="23"/>
       <c r="H14" s="19"/>
-      <c r="I14" s="46" t="str">
+      <c r="I14" s="53" t="str">
         <f t="shared" ref="I14:I24" si="0">IF(NOT(G14*F14=0), G14*F14, "")</f>
         <v/>
       </c>
-      <c r="J14" s="47"/>
+      <c r="J14" s="54"/>
     </row>
     <row r="15" spans="2:10" ht="20.100000000000001" customHeight="1">
       <c r="B15" s="16">
         <v>3</v>
       </c>
-      <c r="C15" s="48"/>
-      <c r="D15" s="48"/>
+      <c r="C15" s="52"/>
+      <c r="D15" s="52"/>
       <c r="E15" s="9"/>
       <c r="F15" s="10"/>
       <c r="G15" s="22"/>
       <c r="H15" s="19"/>
-      <c r="I15" s="46" t="str">
+      <c r="I15" s="53" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="J15" s="47"/>
+      <c r="J15" s="54"/>
     </row>
     <row r="16" spans="2:10" ht="20.100000000000001" customHeight="1">
       <c r="B16" s="16">
         <v>4</v>
       </c>
-      <c r="C16" s="48"/>
-      <c r="D16" s="48"/>
+      <c r="C16" s="52"/>
+      <c r="D16" s="52"/>
       <c r="E16" s="9"/>
       <c r="F16" s="10"/>
       <c r="G16" s="22"/>
       <c r="H16" s="19"/>
-      <c r="I16" s="46" t="str">
+      <c r="I16" s="53" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="J16" s="47"/>
+      <c r="J16" s="54"/>
     </row>
     <row r="17" spans="2:10" ht="20.100000000000001" customHeight="1">
       <c r="B17" s="16">
         <v>5</v>
       </c>
-      <c r="C17" s="48"/>
-      <c r="D17" s="48"/>
+      <c r="C17" s="52"/>
+      <c r="D17" s="52"/>
       <c r="E17" s="9"/>
       <c r="F17" s="10"/>
       <c r="G17" s="22"/>
       <c r="H17" s="19"/>
-      <c r="I17" s="46" t="str">
+      <c r="I17" s="53" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="J17" s="47"/>
+      <c r="J17" s="54"/>
     </row>
     <row r="18" spans="2:10" ht="20.100000000000001" customHeight="1">
       <c r="B18" s="16">
         <v>6</v>
       </c>
-      <c r="C18" s="48"/>
-      <c r="D18" s="48"/>
+      <c r="C18" s="52"/>
+      <c r="D18" s="52"/>
       <c r="E18" s="9"/>
       <c r="F18" s="10"/>
       <c r="G18" s="22"/>
       <c r="H18" s="19"/>
-      <c r="I18" s="46" t="str">
+      <c r="I18" s="53" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="J18" s="47"/>
+      <c r="J18" s="54"/>
     </row>
     <row r="19" spans="2:10" ht="20.100000000000001" customHeight="1">
       <c r="B19" s="16">
         <v>7</v>
       </c>
-      <c r="C19" s="48"/>
-      <c r="D19" s="48"/>
+      <c r="C19" s="52"/>
+      <c r="D19" s="52"/>
       <c r="E19" s="9"/>
       <c r="F19" s="10"/>
       <c r="G19" s="22"/>
       <c r="H19" s="19"/>
-      <c r="I19" s="46" t="str">
+      <c r="I19" s="53" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="J19" s="47"/>
+      <c r="J19" s="54"/>
     </row>
     <row r="20" spans="2:10" ht="20.100000000000001" customHeight="1">
       <c r="B20" s="16">
         <v>8</v>
       </c>
-      <c r="C20" s="48"/>
-      <c r="D20" s="48"/>
+      <c r="C20" s="52"/>
+      <c r="D20" s="52"/>
       <c r="E20" s="9"/>
       <c r="F20" s="10"/>
       <c r="G20" s="22"/>
       <c r="H20" s="19"/>
-      <c r="I20" s="46" t="str">
+      <c r="I20" s="53" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="J20" s="47"/>
+      <c r="J20" s="54"/>
     </row>
     <row r="21" spans="2:10" ht="20.100000000000001" customHeight="1">
       <c r="B21" s="16">
         <v>9</v>
       </c>
-      <c r="C21" s="48"/>
-      <c r="D21" s="48"/>
+      <c r="C21" s="52"/>
+      <c r="D21" s="52"/>
       <c r="E21" s="9"/>
       <c r="F21" s="10"/>
       <c r="G21" s="22"/>
       <c r="H21" s="19"/>
-      <c r="I21" s="46" t="str">
+      <c r="I21" s="53" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="J21" s="47"/>
+      <c r="J21" s="54"/>
     </row>
     <row r="22" spans="2:10" ht="20.100000000000001" customHeight="1">
       <c r="B22" s="16">
         <v>10</v>
       </c>
-      <c r="C22" s="48"/>
-      <c r="D22" s="48"/>
+      <c r="C22" s="52"/>
+      <c r="D22" s="52"/>
       <c r="E22" s="9"/>
       <c r="F22" s="10"/>
       <c r="G22" s="22"/>
       <c r="H22" s="19"/>
-      <c r="I22" s="46" t="str">
+      <c r="I22" s="53" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="J22" s="47"/>
+      <c r="J22" s="54"/>
     </row>
     <row r="23" spans="2:10" ht="20.100000000000001" customHeight="1">
       <c r="B23" s="16">
         <v>11</v>
       </c>
-      <c r="C23" s="74"/>
-      <c r="D23" s="75"/>
+      <c r="C23" s="71"/>
+      <c r="D23" s="72"/>
       <c r="E23" s="9"/>
       <c r="F23" s="10"/>
       <c r="G23" s="22"/>
       <c r="H23" s="19"/>
-      <c r="I23" s="46" t="str">
+      <c r="I23" s="53" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="J23" s="47"/>
+      <c r="J23" s="54"/>
     </row>
     <row r="24" spans="2:10" ht="20.100000000000001" customHeight="1">
       <c r="B24" s="16">
         <v>12</v>
       </c>
-      <c r="C24" s="48"/>
-      <c r="D24" s="48"/>
+      <c r="C24" s="52"/>
+      <c r="D24" s="52"/>
       <c r="E24" s="9"/>
       <c r="F24" s="10"/>
       <c r="G24" s="22"/>
       <c r="H24" s="19"/>
-      <c r="I24" s="46" t="str">
+      <c r="I24" s="53" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="J24" s="47"/>
+      <c r="J24" s="54"/>
     </row>
     <row r="25" spans="2:10" ht="30" customHeight="1">
-      <c r="B25" s="49" t="s">
+      <c r="B25" s="55" t="s">
         <v>9</v>
       </c>
-      <c r="C25" s="50"/>
-      <c r="D25" s="50"/>
-      <c r="E25" s="50"/>
-      <c r="F25" s="50"/>
-      <c r="G25" s="50"/>
-      <c r="H25" s="51"/>
-      <c r="I25" s="52">
+      <c r="C25" s="56"/>
+      <c r="D25" s="56"/>
+      <c r="E25" s="56"/>
+      <c r="F25" s="56"/>
+      <c r="G25" s="56"/>
+      <c r="H25" s="57"/>
+      <c r="I25" s="58">
         <f>SUM(I13:J24)</f>
         <v>3300000</v>
       </c>
-      <c r="J25" s="53"/>
+      <c r="J25" s="59"/>
     </row>
     <row r="26" spans="2:10" ht="30" customHeight="1">
-      <c r="B26" s="54" t="s">
+      <c r="B26" s="60" t="s">
         <v>12</v>
       </c>
-      <c r="C26" s="50"/>
-      <c r="D26" s="50"/>
-      <c r="E26" s="50"/>
-      <c r="F26" s="50"/>
-      <c r="G26" s="50"/>
-      <c r="H26" s="51"/>
-      <c r="I26" s="55"/>
-      <c r="J26" s="56"/>
+      <c r="C26" s="56"/>
+      <c r="D26" s="56"/>
+      <c r="E26" s="56"/>
+      <c r="F26" s="56"/>
+      <c r="G26" s="56"/>
+      <c r="H26" s="57"/>
+      <c r="I26" s="61"/>
+      <c r="J26" s="62"/>
     </row>
     <row r="27" spans="2:10" ht="30" customHeight="1" thickBot="1">
-      <c r="B27" s="57" t="s">
+      <c r="B27" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="C27" s="58"/>
-      <c r="D27" s="58"/>
-      <c r="E27" s="58"/>
-      <c r="F27" s="58"/>
-      <c r="G27" s="58"/>
-      <c r="H27" s="59"/>
-      <c r="I27" s="60">
+      <c r="C27" s="42"/>
+      <c r="D27" s="42"/>
+      <c r="E27" s="42"/>
+      <c r="F27" s="42"/>
+      <c r="G27" s="42"/>
+      <c r="H27" s="43"/>
+      <c r="I27" s="44">
         <f>I25+I26</f>
         <v>3300000</v>
       </c>
-      <c r="J27" s="61"/>
+      <c r="J27" s="45"/>
     </row>
     <row r="28" spans="2:10" ht="44.25" customHeight="1" thickBot="1">
-      <c r="B28" s="62"/>
-      <c r="C28" s="63"/>
-      <c r="D28" s="63"/>
-      <c r="E28" s="63"/>
-      <c r="F28" s="63"/>
-      <c r="G28" s="63"/>
-      <c r="H28" s="63"/>
-      <c r="I28" s="63"/>
-      <c r="J28" s="64"/>
+      <c r="B28" s="75"/>
+      <c r="C28" s="76"/>
+      <c r="D28" s="76"/>
+      <c r="E28" s="76"/>
+      <c r="F28" s="76"/>
+      <c r="G28" s="76"/>
+      <c r="H28" s="76"/>
+      <c r="I28" s="76"/>
+      <c r="J28" s="77"/>
     </row>
     <row r="29" spans="2:10" ht="17.25" customHeight="1">
       <c r="D29" s="1"/>
@@ -3429,9 +3429,9 @@
       <c r="G29" s="1"/>
     </row>
     <row r="30" spans="2:10" ht="48" customHeight="1">
-      <c r="B30" s="65"/>
-      <c r="C30" s="65"/>
-      <c r="D30" s="65"/>
+      <c r="B30" s="46"/>
+      <c r="C30" s="46"/>
+      <c r="D30" s="46"/>
       <c r="E30" s="29"/>
       <c r="F30" s="32"/>
       <c r="G30" s="33" t="s">
@@ -3440,37 +3440,37 @@
       <c r="H30" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="I30" s="68" t="s">
+      <c r="I30" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="J30" s="68"/>
+      <c r="J30" s="50"/>
     </row>
     <row r="31" spans="2:10" ht="36.75" customHeight="1">
       <c r="B31" s="30"/>
-      <c r="C31" s="66"/>
-      <c r="D31" s="67"/>
+      <c r="C31" s="47"/>
+      <c r="D31" s="48"/>
       <c r="E31" s="30"/>
-      <c r="F31" s="66"/>
-      <c r="G31" s="45"/>
-      <c r="H31" s="45"/>
-      <c r="I31" s="69"/>
-      <c r="J31" s="69"/>
+      <c r="F31" s="47"/>
+      <c r="G31" s="49"/>
+      <c r="H31" s="49"/>
+      <c r="I31" s="51"/>
+      <c r="J31" s="51"/>
     </row>
     <row r="32" spans="2:10" ht="30" customHeight="1">
       <c r="B32" s="28"/>
-      <c r="C32" s="70"/>
-      <c r="D32" s="70"/>
+      <c r="C32" s="39"/>
+      <c r="D32" s="39"/>
       <c r="E32" s="27"/>
-      <c r="F32" s="66"/>
-      <c r="G32" s="45"/>
-      <c r="H32" s="45"/>
-      <c r="I32" s="69"/>
-      <c r="J32" s="69"/>
+      <c r="F32" s="47"/>
+      <c r="G32" s="49"/>
+      <c r="H32" s="49"/>
+      <c r="I32" s="51"/>
+      <c r="J32" s="51"/>
     </row>
     <row r="33" spans="2:10" ht="30" customHeight="1">
       <c r="B33" s="6"/>
-      <c r="C33" s="70"/>
-      <c r="D33" s="70"/>
+      <c r="C33" s="39"/>
+      <c r="D33" s="39"/>
       <c r="E33" s="27"/>
       <c r="F33" s="20"/>
       <c r="G33" s="20"/>
@@ -3480,8 +3480,8 @@
     </row>
     <row r="34" spans="2:10" ht="30" customHeight="1">
       <c r="B34" s="6"/>
-      <c r="C34" s="70"/>
-      <c r="D34" s="70"/>
+      <c r="C34" s="39"/>
+      <c r="D34" s="39"/>
       <c r="E34" s="27"/>
       <c r="F34" s="20"/>
       <c r="G34" s="20"/>
@@ -3491,8 +3491,8 @@
     </row>
     <row r="35" spans="2:10" ht="30" customHeight="1">
       <c r="B35" s="6"/>
-      <c r="C35" s="70"/>
-      <c r="D35" s="70"/>
+      <c r="C35" s="39"/>
+      <c r="D35" s="39"/>
       <c r="E35" s="27"/>
       <c r="F35" s="20"/>
       <c r="G35" s="20"/>
@@ -3502,8 +3502,8 @@
     </row>
     <row r="36" spans="2:10" ht="30" customHeight="1">
       <c r="B36" s="6"/>
-      <c r="C36" s="70"/>
-      <c r="D36" s="70"/>
+      <c r="C36" s="39"/>
+      <c r="D36" s="39"/>
       <c r="E36" s="27"/>
       <c r="F36" s="20"/>
       <c r="G36" s="20"/>
@@ -3513,8 +3513,8 @@
     </row>
     <row r="37" spans="2:10" ht="30" customHeight="1">
       <c r="B37" s="6"/>
-      <c r="C37" s="70"/>
-      <c r="D37" s="70"/>
+      <c r="C37" s="39"/>
+      <c r="D37" s="39"/>
       <c r="E37" s="27"/>
       <c r="F37" s="21"/>
       <c r="G37" s="21"/>
@@ -3524,8 +3524,8 @@
     </row>
     <row r="38" spans="2:10" ht="30" customHeight="1">
       <c r="B38" s="6"/>
-      <c r="C38" s="71"/>
-      <c r="D38" s="71"/>
+      <c r="C38" s="40"/>
+      <c r="D38" s="40"/>
       <c r="E38" s="28"/>
       <c r="F38" s="21"/>
       <c r="G38" s="21"/>
@@ -3535,8 +3535,8 @@
     </row>
     <row r="39" spans="2:10" ht="30" customHeight="1">
       <c r="B39" s="6"/>
-      <c r="C39" s="71"/>
-      <c r="D39" s="71"/>
+      <c r="C39" s="40"/>
+      <c r="D39" s="40"/>
       <c r="E39" s="28"/>
       <c r="F39" s="21"/>
       <c r="G39" s="21"/>
@@ -3546,8 +3546,8 @@
     </row>
     <row r="40" spans="2:10" ht="30" customHeight="1">
       <c r="B40" s="6"/>
-      <c r="C40" s="71"/>
-      <c r="D40" s="71"/>
+      <c r="C40" s="40"/>
+      <c r="D40" s="40"/>
       <c r="E40" s="28"/>
       <c r="F40" s="21"/>
       <c r="G40" s="21"/>
@@ -3579,6 +3579,43 @@
     </row>
   </sheetData>
   <mergeCells count="53">
+    <mergeCell ref="C1:J1"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B9:G9"/>
+    <mergeCell ref="B10:G10"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="B25:H25"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="B26:H26"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="F31:F32"/>
+    <mergeCell ref="G31:G32"/>
+    <mergeCell ref="H31:H32"/>
+    <mergeCell ref="I31:J32"/>
+    <mergeCell ref="B27:H27"/>
+    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="B28:J28"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="I30:J30"/>
     <mergeCell ref="C38:D38"/>
     <mergeCell ref="C39:D39"/>
     <mergeCell ref="C40:D40"/>
@@ -3595,43 +3632,6 @@
     <mergeCell ref="C35:D35"/>
     <mergeCell ref="C36:D36"/>
     <mergeCell ref="C37:D37"/>
-    <mergeCell ref="B27:H27"/>
-    <mergeCell ref="I27:J27"/>
-    <mergeCell ref="B28:J28"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="F31:F32"/>
-    <mergeCell ref="G31:G32"/>
-    <mergeCell ref="H31:H32"/>
-    <mergeCell ref="I31:J32"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="B25:H25"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="B26:H26"/>
-    <mergeCell ref="I26:J26"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="C1:J1"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="B9:G9"/>
-    <mergeCell ref="B10:G10"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="I12:J12"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.12" right="0.16" top="0.22" bottom="0.12" header="0.3" footer="0.3"/>
@@ -3662,16 +3662,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:10" ht="54" customHeight="1">
-      <c r="C1" s="37" t="s">
+      <c r="C1" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
-      <c r="J1" s="38"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
+      <c r="H1" s="64"/>
+      <c r="I1" s="64"/>
+      <c r="J1" s="64"/>
     </row>
     <row r="2" spans="2:10" ht="21.75" customHeight="1">
       <c r="C2" s="36"/>
@@ -3681,7 +3681,7 @@
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
-      <c r="J2" s="73" t="s">
+      <c r="J2" s="38" t="s">
         <v>23</v>
       </c>
     </row>
@@ -3693,7 +3693,7 @@
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
-      <c r="J3" s="72" t="s">
+      <c r="J3" s="37" t="s">
         <v>24</v>
       </c>
     </row>
@@ -3739,9 +3739,9 @@
       <c r="J6" s="11"/>
     </row>
     <row r="7" spans="2:10" ht="18.75" customHeight="1">
-      <c r="B7" s="39"/>
-      <c r="C7" s="39"/>
-      <c r="D7" s="39"/>
+      <c r="B7" s="65"/>
+      <c r="C7" s="65"/>
+      <c r="D7" s="65"/>
       <c r="E7" s="2"/>
       <c r="F7" s="5"/>
       <c r="G7" s="5"/>
@@ -3759,26 +3759,26 @@
       <c r="I8" s="6"/>
     </row>
     <row r="9" spans="2:10" s="8" customFormat="1" ht="18" customHeight="1">
-      <c r="B9" s="40" t="s">
+      <c r="B9" s="66" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="40"/>
-      <c r="D9" s="40"/>
-      <c r="E9" s="40"/>
-      <c r="F9" s="40"/>
-      <c r="G9" s="40"/>
+      <c r="C9" s="66"/>
+      <c r="D9" s="66"/>
+      <c r="E9" s="66"/>
+      <c r="F9" s="66"/>
+      <c r="G9" s="66"/>
       <c r="H9" s="17"/>
       <c r="I9" s="17"/>
     </row>
     <row r="10" spans="2:10" ht="18" customHeight="1">
-      <c r="B10" s="41" t="s">
+      <c r="B10" s="67" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="41"/>
-      <c r="D10" s="41"/>
-      <c r="E10" s="41"/>
-      <c r="F10" s="41"/>
-      <c r="G10" s="41"/>
+      <c r="C10" s="67"/>
+      <c r="D10" s="67"/>
+      <c r="E10" s="67"/>
+      <c r="F10" s="67"/>
+      <c r="G10" s="67"/>
     </row>
     <row r="11" spans="2:10" ht="18" customHeight="1" thickBot="1">
       <c r="D11" s="1"/>
@@ -3790,10 +3790,10 @@
       <c r="B12" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="C12" s="42" t="s">
+      <c r="C12" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="D12" s="43"/>
+      <c r="D12" s="69"/>
       <c r="E12" s="13" t="s">
         <v>6</v>
       </c>
@@ -3806,19 +3806,19 @@
       <c r="H12" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="I12" s="42" t="s">
+      <c r="I12" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="J12" s="44"/>
+      <c r="J12" s="70"/>
     </row>
     <row r="13" spans="2:10" ht="16.5">
       <c r="B13" s="16">
         <v>1</v>
       </c>
-      <c r="C13" s="45" t="s">
+      <c r="C13" s="49" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="45"/>
+      <c r="D13" s="49"/>
       <c r="E13" s="9" t="s">
         <v>13</v>
       </c>
@@ -3829,323 +3829,323 @@
         <v>6600</v>
       </c>
       <c r="H13" s="19"/>
-      <c r="I13" s="46">
+      <c r="I13" s="53">
         <f>IF(NOT(G13*F13=0), G13*F13, "")</f>
         <v>3300000</v>
       </c>
-      <c r="J13" s="47"/>
+      <c r="J13" s="54"/>
     </row>
     <row r="14" spans="2:10" ht="21" customHeight="1">
       <c r="B14" s="16">
         <v>2</v>
       </c>
-      <c r="C14" s="76"/>
-      <c r="D14" s="77"/>
+      <c r="C14" s="73"/>
+      <c r="D14" s="74"/>
       <c r="E14" s="9"/>
       <c r="F14" s="10"/>
       <c r="G14" s="23"/>
       <c r="H14" s="19"/>
-      <c r="I14" s="46" t="str">
+      <c r="I14" s="53" t="str">
         <f>IF(NOT(G14*F14=0), G14*F14, "")</f>
         <v/>
       </c>
-      <c r="J14" s="47"/>
+      <c r="J14" s="54"/>
     </row>
     <row r="15" spans="2:10" ht="20.100000000000001" customHeight="1">
       <c r="B15" s="16">
         <v>3</v>
       </c>
-      <c r="C15" s="74"/>
-      <c r="D15" s="75"/>
+      <c r="C15" s="71"/>
+      <c r="D15" s="72"/>
       <c r="E15" s="9"/>
       <c r="F15" s="10"/>
       <c r="G15" s="22"/>
       <c r="H15" s="19"/>
-      <c r="I15" s="46" t="str">
+      <c r="I15" s="53" t="str">
         <f t="shared" ref="I15:I21" si="0">IF(NOT(G15*F15=0), G15*F15, "")</f>
         <v/>
       </c>
-      <c r="J15" s="47"/>
+      <c r="J15" s="54"/>
     </row>
     <row r="16" spans="2:10" ht="21" customHeight="1">
       <c r="B16" s="16">
         <v>4</v>
       </c>
-      <c r="C16" s="45"/>
-      <c r="D16" s="45"/>
+      <c r="C16" s="49"/>
+      <c r="D16" s="49"/>
       <c r="E16" s="9"/>
       <c r="F16" s="10"/>
       <c r="G16" s="23"/>
       <c r="H16" s="19"/>
-      <c r="I16" s="46" t="str">
+      <c r="I16" s="53" t="str">
         <f>IF(NOT(G16*F16=0), G16*F16, "")</f>
         <v/>
       </c>
-      <c r="J16" s="47"/>
+      <c r="J16" s="54"/>
     </row>
     <row r="17" spans="2:10" ht="20.100000000000001" customHeight="1">
       <c r="B17" s="16">
         <v>5</v>
       </c>
-      <c r="C17" s="48"/>
-      <c r="D17" s="48"/>
+      <c r="C17" s="52"/>
+      <c r="D17" s="52"/>
       <c r="E17" s="9"/>
       <c r="F17" s="10"/>
       <c r="G17" s="22"/>
       <c r="H17" s="19"/>
-      <c r="I17" s="46" t="str">
+      <c r="I17" s="53" t="str">
         <f t="shared" ref="I17:I19" si="1">IF(NOT(G17*F17=0), G17*F17, "")</f>
         <v/>
       </c>
-      <c r="J17" s="47"/>
+      <c r="J17" s="54"/>
     </row>
     <row r="18" spans="2:10" ht="20.100000000000001" customHeight="1">
       <c r="B18" s="16">
         <v>6</v>
       </c>
-      <c r="C18" s="48"/>
-      <c r="D18" s="48"/>
+      <c r="C18" s="52"/>
+      <c r="D18" s="52"/>
       <c r="E18" s="9"/>
       <c r="F18" s="10"/>
       <c r="G18" s="22"/>
       <c r="H18" s="19"/>
-      <c r="I18" s="46" t="str">
+      <c r="I18" s="53" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J18" s="47"/>
+      <c r="J18" s="54"/>
     </row>
     <row r="19" spans="2:10" ht="20.100000000000001" customHeight="1">
       <c r="B19" s="16">
         <v>7</v>
       </c>
-      <c r="C19" s="48"/>
-      <c r="D19" s="48"/>
+      <c r="C19" s="52"/>
+      <c r="D19" s="52"/>
       <c r="E19" s="9"/>
       <c r="F19" s="10"/>
       <c r="G19" s="22"/>
       <c r="H19" s="19"/>
-      <c r="I19" s="46" t="str">
+      <c r="I19" s="53" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J19" s="47"/>
+      <c r="J19" s="54"/>
     </row>
     <row r="20" spans="2:10" ht="20.100000000000001" customHeight="1">
       <c r="B20" s="16">
         <v>8</v>
       </c>
-      <c r="C20" s="74"/>
-      <c r="D20" s="75"/>
+      <c r="C20" s="71"/>
+      <c r="D20" s="72"/>
       <c r="E20" s="9"/>
       <c r="F20" s="10"/>
       <c r="G20" s="22"/>
       <c r="H20" s="19"/>
-      <c r="I20" s="46" t="str">
+      <c r="I20" s="53" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="J20" s="47"/>
+      <c r="J20" s="54"/>
     </row>
     <row r="21" spans="2:10" ht="20.100000000000001" customHeight="1">
       <c r="B21" s="16">
         <v>9</v>
       </c>
-      <c r="C21" s="74"/>
-      <c r="D21" s="75"/>
+      <c r="C21" s="71"/>
+      <c r="D21" s="72"/>
       <c r="E21" s="9"/>
       <c r="F21" s="10"/>
       <c r="G21" s="22"/>
       <c r="H21" s="19"/>
-      <c r="I21" s="46" t="str">
+      <c r="I21" s="53" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="J21" s="47"/>
+      <c r="J21" s="54"/>
     </row>
     <row r="22" spans="2:10" ht="21" customHeight="1">
       <c r="B22" s="16">
         <v>10</v>
       </c>
-      <c r="C22" s="45"/>
-      <c r="D22" s="45"/>
+      <c r="C22" s="49"/>
+      <c r="D22" s="49"/>
       <c r="E22" s="9"/>
       <c r="F22" s="10"/>
       <c r="G22" s="23"/>
       <c r="H22" s="19"/>
-      <c r="I22" s="46" t="str">
+      <c r="I22" s="53" t="str">
         <f>IF(NOT(G22*F22=0), G22*F22, "")</f>
         <v/>
       </c>
-      <c r="J22" s="47"/>
+      <c r="J22" s="54"/>
     </row>
     <row r="23" spans="2:10" ht="20.100000000000001" customHeight="1">
       <c r="B23" s="16">
         <v>11</v>
       </c>
-      <c r="C23" s="48"/>
-      <c r="D23" s="48"/>
+      <c r="C23" s="52"/>
+      <c r="D23" s="52"/>
       <c r="E23" s="9"/>
       <c r="F23" s="10"/>
       <c r="G23" s="22"/>
       <c r="H23" s="19"/>
-      <c r="I23" s="46" t="str">
+      <c r="I23" s="53" t="str">
         <f t="shared" ref="I23:I29" si="2">IF(NOT(G23*F23=0), G23*F23, "")</f>
         <v/>
       </c>
-      <c r="J23" s="47"/>
+      <c r="J23" s="54"/>
     </row>
     <row r="24" spans="2:10" ht="20.100000000000001" customHeight="1">
       <c r="B24" s="16">
         <v>12</v>
       </c>
-      <c r="C24" s="48"/>
-      <c r="D24" s="48"/>
+      <c r="C24" s="52"/>
+      <c r="D24" s="52"/>
       <c r="E24" s="9"/>
       <c r="F24" s="10"/>
       <c r="G24" s="22"/>
       <c r="H24" s="19"/>
-      <c r="I24" s="46" t="str">
+      <c r="I24" s="53" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J24" s="47"/>
+      <c r="J24" s="54"/>
     </row>
     <row r="25" spans="2:10" ht="20.100000000000001" customHeight="1">
       <c r="B25" s="16">
         <v>13</v>
       </c>
-      <c r="C25" s="48"/>
-      <c r="D25" s="48"/>
+      <c r="C25" s="52"/>
+      <c r="D25" s="52"/>
       <c r="E25" s="9"/>
       <c r="F25" s="10"/>
       <c r="G25" s="22"/>
       <c r="H25" s="19"/>
-      <c r="I25" s="46" t="str">
+      <c r="I25" s="53" t="str">
         <f t="shared" ref="I25:I26" si="3">IF(NOT(G25*F25=0), G25*F25, "")</f>
         <v/>
       </c>
-      <c r="J25" s="47"/>
+      <c r="J25" s="54"/>
     </row>
     <row r="26" spans="2:10" ht="20.100000000000001" customHeight="1">
       <c r="B26" s="16">
         <v>14</v>
       </c>
-      <c r="C26" s="48"/>
-      <c r="D26" s="48"/>
+      <c r="C26" s="52"/>
+      <c r="D26" s="52"/>
       <c r="E26" s="9"/>
       <c r="F26" s="10"/>
       <c r="G26" s="22"/>
       <c r="H26" s="19"/>
-      <c r="I26" s="46" t="str">
+      <c r="I26" s="53" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J26" s="47"/>
+      <c r="J26" s="54"/>
     </row>
     <row r="27" spans="2:10" ht="20.100000000000001" customHeight="1">
       <c r="B27" s="16">
         <v>15</v>
       </c>
-      <c r="C27" s="48"/>
-      <c r="D27" s="48"/>
+      <c r="C27" s="52"/>
+      <c r="D27" s="52"/>
       <c r="E27" s="9"/>
       <c r="F27" s="10"/>
       <c r="G27" s="22"/>
       <c r="H27" s="19"/>
-      <c r="I27" s="46" t="str">
+      <c r="I27" s="53" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J27" s="47"/>
+      <c r="J27" s="54"/>
     </row>
     <row r="28" spans="2:10" ht="20.100000000000001" customHeight="1">
       <c r="B28" s="16">
         <v>16</v>
       </c>
-      <c r="C28" s="48"/>
-      <c r="D28" s="48"/>
+      <c r="C28" s="52"/>
+      <c r="D28" s="52"/>
       <c r="E28" s="9"/>
       <c r="F28" s="10"/>
       <c r="G28" s="22"/>
       <c r="H28" s="19"/>
-      <c r="I28" s="46" t="str">
+      <c r="I28" s="53" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J28" s="47"/>
+      <c r="J28" s="54"/>
     </row>
     <row r="29" spans="2:10" ht="20.100000000000001" customHeight="1">
       <c r="B29" s="16">
         <v>17</v>
       </c>
-      <c r="C29" s="48"/>
-      <c r="D29" s="48"/>
+      <c r="C29" s="52"/>
+      <c r="D29" s="52"/>
       <c r="E29" s="9"/>
       <c r="F29" s="10"/>
       <c r="G29" s="22"/>
       <c r="H29" s="19"/>
-      <c r="I29" s="46" t="str">
+      <c r="I29" s="53" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J29" s="47"/>
+      <c r="J29" s="54"/>
     </row>
     <row r="30" spans="2:10" ht="30" customHeight="1">
-      <c r="B30" s="49" t="s">
+      <c r="B30" s="55" t="s">
         <v>9</v>
       </c>
-      <c r="C30" s="50"/>
-      <c r="D30" s="50"/>
-      <c r="E30" s="50"/>
-      <c r="F30" s="50"/>
-      <c r="G30" s="50"/>
-      <c r="H30" s="51"/>
-      <c r="I30" s="52">
+      <c r="C30" s="56"/>
+      <c r="D30" s="56"/>
+      <c r="E30" s="56"/>
+      <c r="F30" s="56"/>
+      <c r="G30" s="56"/>
+      <c r="H30" s="57"/>
+      <c r="I30" s="58">
         <f>SUM(I13:J29)</f>
         <v>3300000</v>
       </c>
-      <c r="J30" s="53"/>
+      <c r="J30" s="59"/>
     </row>
     <row r="31" spans="2:10" ht="30" customHeight="1">
-      <c r="B31" s="54" t="s">
+      <c r="B31" s="60" t="s">
         <v>12</v>
       </c>
-      <c r="C31" s="50"/>
-      <c r="D31" s="50"/>
-      <c r="E31" s="50"/>
-      <c r="F31" s="50"/>
-      <c r="G31" s="50"/>
-      <c r="H31" s="51"/>
-      <c r="I31" s="55"/>
-      <c r="J31" s="56"/>
+      <c r="C31" s="56"/>
+      <c r="D31" s="56"/>
+      <c r="E31" s="56"/>
+      <c r="F31" s="56"/>
+      <c r="G31" s="56"/>
+      <c r="H31" s="57"/>
+      <c r="I31" s="61"/>
+      <c r="J31" s="62"/>
     </row>
     <row r="32" spans="2:10" ht="30" customHeight="1" thickBot="1">
-      <c r="B32" s="57" t="s">
+      <c r="B32" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="C32" s="58"/>
-      <c r="D32" s="58"/>
-      <c r="E32" s="58"/>
-      <c r="F32" s="58"/>
-      <c r="G32" s="58"/>
-      <c r="H32" s="59"/>
-      <c r="I32" s="60">
+      <c r="C32" s="42"/>
+      <c r="D32" s="42"/>
+      <c r="E32" s="42"/>
+      <c r="F32" s="42"/>
+      <c r="G32" s="42"/>
+      <c r="H32" s="43"/>
+      <c r="I32" s="44">
         <f>I30+I31</f>
         <v>3300000</v>
       </c>
-      <c r="J32" s="61"/>
+      <c r="J32" s="45"/>
     </row>
     <row r="33" spans="2:10" ht="44.25" customHeight="1" thickBot="1">
-      <c r="B33" s="62"/>
-      <c r="C33" s="63"/>
-      <c r="D33" s="63"/>
-      <c r="E33" s="63"/>
-      <c r="F33" s="63"/>
-      <c r="G33" s="63"/>
-      <c r="H33" s="63"/>
-      <c r="I33" s="63"/>
-      <c r="J33" s="64"/>
+      <c r="B33" s="75"/>
+      <c r="C33" s="76"/>
+      <c r="D33" s="76"/>
+      <c r="E33" s="76"/>
+      <c r="F33" s="76"/>
+      <c r="G33" s="76"/>
+      <c r="H33" s="76"/>
+      <c r="I33" s="76"/>
+      <c r="J33" s="77"/>
     </row>
     <row r="34" spans="2:10" ht="17.25" customHeight="1">
       <c r="D34" s="1"/>
@@ -4154,9 +4154,9 @@
       <c r="G34" s="1"/>
     </row>
     <row r="35" spans="2:10" ht="48" customHeight="1">
-      <c r="B35" s="65"/>
-      <c r="C35" s="65"/>
-      <c r="D35" s="65"/>
+      <c r="B35" s="46"/>
+      <c r="C35" s="46"/>
+      <c r="D35" s="46"/>
       <c r="E35" s="29"/>
       <c r="F35" s="32"/>
       <c r="G35" s="33" t="s">
@@ -4165,37 +4165,37 @@
       <c r="H35" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="I35" s="68" t="s">
+      <c r="I35" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="J35" s="68"/>
+      <c r="J35" s="50"/>
     </row>
     <row r="36" spans="2:10" ht="36.75" customHeight="1">
       <c r="B36" s="30"/>
-      <c r="C36" s="66"/>
-      <c r="D36" s="67"/>
+      <c r="C36" s="47"/>
+      <c r="D36" s="48"/>
       <c r="E36" s="30"/>
-      <c r="F36" s="66"/>
-      <c r="G36" s="45"/>
-      <c r="H36" s="45"/>
-      <c r="I36" s="69"/>
-      <c r="J36" s="69"/>
+      <c r="F36" s="47"/>
+      <c r="G36" s="49"/>
+      <c r="H36" s="49"/>
+      <c r="I36" s="51"/>
+      <c r="J36" s="51"/>
     </row>
     <row r="37" spans="2:10" ht="30" customHeight="1">
       <c r="B37" s="28"/>
-      <c r="C37" s="70"/>
-      <c r="D37" s="70"/>
+      <c r="C37" s="39"/>
+      <c r="D37" s="39"/>
       <c r="E37" s="27"/>
-      <c r="F37" s="66"/>
-      <c r="G37" s="45"/>
-      <c r="H37" s="45"/>
-      <c r="I37" s="69"/>
-      <c r="J37" s="69"/>
+      <c r="F37" s="47"/>
+      <c r="G37" s="49"/>
+      <c r="H37" s="49"/>
+      <c r="I37" s="51"/>
+      <c r="J37" s="51"/>
     </row>
     <row r="38" spans="2:10" ht="30" customHeight="1">
       <c r="B38" s="6"/>
-      <c r="C38" s="70"/>
-      <c r="D38" s="70"/>
+      <c r="C38" s="39"/>
+      <c r="D38" s="39"/>
       <c r="E38" s="27"/>
       <c r="F38" s="20"/>
       <c r="G38" s="20"/>
@@ -4205,8 +4205,8 @@
     </row>
     <row r="39" spans="2:10" ht="30" customHeight="1">
       <c r="B39" s="6"/>
-      <c r="C39" s="70"/>
-      <c r="D39" s="70"/>
+      <c r="C39" s="39"/>
+      <c r="D39" s="39"/>
       <c r="E39" s="27"/>
       <c r="F39" s="20"/>
       <c r="G39" s="20"/>
@@ -4216,8 +4216,8 @@
     </row>
     <row r="40" spans="2:10" ht="30" customHeight="1">
       <c r="B40" s="6"/>
-      <c r="C40" s="70"/>
-      <c r="D40" s="70"/>
+      <c r="C40" s="39"/>
+      <c r="D40" s="39"/>
       <c r="E40" s="27"/>
       <c r="F40" s="20"/>
       <c r="G40" s="20"/>
@@ -4227,8 +4227,8 @@
     </row>
     <row r="41" spans="2:10" ht="30" customHeight="1">
       <c r="B41" s="6"/>
-      <c r="C41" s="70"/>
-      <c r="D41" s="70"/>
+      <c r="C41" s="39"/>
+      <c r="D41" s="39"/>
       <c r="E41" s="27"/>
       <c r="F41" s="20"/>
       <c r="G41" s="20"/>
@@ -4238,8 +4238,8 @@
     </row>
     <row r="42" spans="2:10" ht="30" customHeight="1">
       <c r="B42" s="6"/>
-      <c r="C42" s="70"/>
-      <c r="D42" s="70"/>
+      <c r="C42" s="39"/>
+      <c r="D42" s="39"/>
       <c r="E42" s="27"/>
       <c r="F42" s="21"/>
       <c r="G42" s="21"/>
@@ -4249,8 +4249,8 @@
     </row>
     <row r="43" spans="2:10" ht="30" customHeight="1">
       <c r="B43" s="6"/>
-      <c r="C43" s="71"/>
-      <c r="D43" s="71"/>
+      <c r="C43" s="40"/>
+      <c r="D43" s="40"/>
       <c r="E43" s="28"/>
       <c r="F43" s="21"/>
       <c r="G43" s="21"/>
@@ -4260,8 +4260,8 @@
     </row>
     <row r="44" spans="2:10" ht="30" customHeight="1">
       <c r="B44" s="6"/>
-      <c r="C44" s="71"/>
-      <c r="D44" s="71"/>
+      <c r="C44" s="40"/>
+      <c r="D44" s="40"/>
       <c r="E44" s="28"/>
       <c r="F44" s="21"/>
       <c r="G44" s="21"/>
@@ -4271,8 +4271,8 @@
     </row>
     <row r="45" spans="2:10" ht="30" customHeight="1">
       <c r="B45" s="6"/>
-      <c r="C45" s="71"/>
-      <c r="D45" s="71"/>
+      <c r="C45" s="40"/>
+      <c r="D45" s="40"/>
       <c r="E45" s="28"/>
       <c r="F45" s="21"/>
       <c r="G45" s="21"/>
@@ -4304,43 +4304,22 @@
     </row>
   </sheetData>
   <mergeCells count="63">
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="C44:D44"/>
-    <mergeCell ref="C45:D45"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="C40:D40"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="B32:H32"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="B33:J33"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="F36:F37"/>
-    <mergeCell ref="G36:G37"/>
-    <mergeCell ref="H36:H37"/>
-    <mergeCell ref="I36:J37"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="B30:H30"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="B31:H31"/>
-    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="C1:J1"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B9:G9"/>
+    <mergeCell ref="B10:G10"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="C20:D20"/>
     <mergeCell ref="C24:D24"/>
     <mergeCell ref="I24:J24"/>
     <mergeCell ref="C27:D27"/>
@@ -4351,22 +4330,43 @@
     <mergeCell ref="I25:J25"/>
     <mergeCell ref="C26:D26"/>
     <mergeCell ref="I26:J26"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C1:J1"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="B9:G9"/>
-    <mergeCell ref="B10:G10"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="B30:H30"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="B31:H31"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="F36:F37"/>
+    <mergeCell ref="G36:G37"/>
+    <mergeCell ref="H36:H37"/>
+    <mergeCell ref="I36:J37"/>
+    <mergeCell ref="B32:H32"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="B33:J33"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="I19:J19"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.12" right="0.16" top="0.22" bottom="0.12" header="0.3" footer="0.3"/>

--- a/app/public/発注フォーム.xlsx
+++ b/app/public/発注フォーム.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\masuda-vinyl-ops\app\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D620FF6-1B75-4B44-B918-9201A746CEBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68B6B7C2-B768-4B4D-A3EC-12BA927535C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2775" yWindow="1410" windowWidth="21600" windowHeight="15870" xr2:uid="{811621DE-664E-4521-9512-F04E9755C0E8}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{811621DE-664E-4521-9512-F04E9755C0E8}"/>
   </bookViews>
   <sheets>
     <sheet name="Duc Phong" sheetId="170" r:id="rId1"/>
     <sheet name="Duc Phong-12" sheetId="171" state="hidden" r:id="rId2"/>
     <sheet name="Duc Phong-17" sheetId="172" state="hidden" r:id="rId3"/>
+    <sheet name="setting" sheetId="173" state="hidden" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Duc Phong'!$A$1:$J$33</definedName>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="26">
   <si>
     <r>
       <rPr>
@@ -504,6 +505,13 @@
   </si>
   <si>
     <t xml:space="preserve">Mã đặt hàng: </t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t xml:space="preserve">MASUDA VINYL VIETNAM
+Lô I Đồng vàng, Khu công nghiệp Đình Trám,
+Phường Nếnh, Thị xã Việt Yên, Tỉnh Bắc Giang
+TELL: 0204-3662-777  FAX:  0204-3662-825                                 </t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -1072,7 +1080,7 @@
     </xf>
     <xf numFmtId="40" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1176,78 +1184,6 @@
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="18" fillId="0" borderId="20" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="18" fillId="0" borderId="21" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="15" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="15" fillId="0" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="18" fillId="0" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="18" fillId="0" borderId="15" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="15" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="15" fillId="0" borderId="16" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1270,6 +1206,87 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="15" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="15" fillId="0" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="18" fillId="0" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="18" fillId="0" borderId="15" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="15" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="15" fillId="0" borderId="16" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="18" fillId="0" borderId="20" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="18" fillId="0" borderId="21" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1282,14 +1299,8 @@
     <xf numFmtId="0" fontId="34" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1326,7 +1337,7 @@
       <xdr:row>9</xdr:row>
       <xdr:rowOff>209551</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp macro="" textlink="setting!A1">
       <xdr:nvSpPr>
         <xdr:cNvPr id="2" name="テキスト ボックス 1">
           <a:extLst>
@@ -1368,199 +1379,20 @@
         <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
         <a:lstStyle/>
         <a:p>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ja-JP" sz="1200" b="0" i="0" u="none" strike="noStrike">
+          <a:fld id="{54ADCDEB-E225-4F83-89AA-87DDFCA62263}" type="TxLink">
+            <a:rPr kumimoji="1" lang="en-US" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
-                <a:schemeClr val="dk1"/>
+                <a:srgbClr val="000000"/>
               </a:solidFill>
-              <a:effectLst/>
               <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:ea typeface="+mn-ea"/>
+              <a:ea typeface="ＭＳ Ｐゴシック"/>
               <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
             </a:rPr>
-            <a:t>MASUDA VINYL VIETNAM</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ja-JP" sz="1200">
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ja-JP" sz="1200" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t>                                   </a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ja-JP" sz="1200" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t>Lô I Đồng vàng, Khu công nghiệp Đình Trám, </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ja-JP" sz="1200">
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ja-JP" sz="1200" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t>                                   Phường</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ja-JP" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ja-JP" sz="1200" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t>Nếnh</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ja-JP" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t>, </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ja-JP" sz="1200" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t>Thị</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ja-JP" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t> xã</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ja-JP" sz="1200" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t> Việt Yên, Tỉnh Bắc Giang</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ja-JP" sz="1200">
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ja-JP" sz="1200" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t>                               </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ja-JP" sz="1200">
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ja-JP" sz="1200" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t>             TELL: 0204-3662-777  FAX</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t>:  0204-3662-825                                </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ja-JP" sz="1100">
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
+            <a:t>MASUDA VINYL VIETNAM
+Lô I Đồng vàng, Khu công nghiệp Đình Trám,
+Phường Nếnh, Thị xã Việt Yên, Tỉnh Bắc Giang
+TELL: 0204-3662-777  FAX:  0204-3662-825                                 </a:t>
+          </a:fld>
           <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
             <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
             <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
@@ -1588,7 +1420,7 @@
       <xdr:row>9</xdr:row>
       <xdr:rowOff>209551</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp macro="" textlink="setting!A1">
       <xdr:nvSpPr>
         <xdr:cNvPr id="2" name="テキスト ボックス 1">
           <a:extLst>
@@ -1630,199 +1462,19 @@
         <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
         <a:lstStyle/>
         <a:p>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ja-JP" sz="1200" b="0" i="0" u="none" strike="noStrike">
+          <a:fld id="{4F13A9F1-EBB2-4C0C-9B28-953C70DFCF11}" type="TxLink">
+            <a:rPr kumimoji="1" lang="en-US" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
-                <a:schemeClr val="dk1"/>
+                <a:srgbClr val="000000"/>
               </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:latin typeface="Times New Roman"/>
+              <a:cs typeface="Times New Roman"/>
             </a:rPr>
-            <a:t>MASUDA VINYL VIETNAM</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ja-JP" sz="1200">
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ja-JP" sz="1200" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t>                                   </a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ja-JP" sz="1200" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t>Lô I Đồng vàng, Khu công nghiệp Đình Trám, </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ja-JP" sz="1200">
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ja-JP" sz="1200" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t>                                   Phường</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ja-JP" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ja-JP" sz="1200" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t>Nếnh</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ja-JP" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t>, </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ja-JP" sz="1200" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t>Thị</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ja-JP" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t> xã</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ja-JP" sz="1200" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t> Việt Yên, Tỉnh Bắc Giang</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ja-JP" sz="1200">
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ja-JP" sz="1200" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t>                               </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ja-JP" sz="1200">
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ja-JP" sz="1200" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t>             TELL: 0204-3662-777  FAX</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t>:  0204-3662-825                                </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ja-JP" sz="1100">
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
+            <a:t>MASUDA VINYL VIETNAM
+Lô I Đồng vàng, Khu công nghiệp Đình Trám,
+Phường Nếnh, Thị xã Việt Yên, Tỉnh Bắc Giang
+TELL: 0204-3662-777  FAX:  0204-3662-825                                 </a:t>
+          </a:fld>
           <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
             <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
             <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
@@ -1850,7 +1502,7 @@
       <xdr:row>9</xdr:row>
       <xdr:rowOff>209551</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp macro="" textlink="setting!A1">
       <xdr:nvSpPr>
         <xdr:cNvPr id="2" name="テキスト ボックス 1">
           <a:extLst>
@@ -1892,199 +1544,19 @@
         <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
         <a:lstStyle/>
         <a:p>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ja-JP" sz="1200" b="0" i="0" u="none" strike="noStrike">
+          <a:fld id="{6F715E33-F450-4957-8EB1-0CFBEFF91E85}" type="TxLink">
+            <a:rPr kumimoji="1" lang="en-US" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
-                <a:schemeClr val="dk1"/>
+                <a:srgbClr val="000000"/>
               </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:latin typeface="Times New Roman"/>
+              <a:cs typeface="Times New Roman"/>
             </a:rPr>
-            <a:t>MASUDA VINYL VIETNAM</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ja-JP" sz="1200">
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ja-JP" sz="1200" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t>                                   </a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ja-JP" sz="1200" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t>Lô I Đồng vàng, Khu công nghiệp Đình Trám, </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ja-JP" sz="1200">
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ja-JP" sz="1200" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t>                                   Phường</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ja-JP" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ja-JP" sz="1200" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t>Nếnh</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ja-JP" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t>, </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ja-JP" sz="1200" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t>Thị</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ja-JP" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t> xã</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ja-JP" sz="1200" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t> Việt Yên, Tỉnh Bắc Giang</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ja-JP" sz="1200">
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ja-JP" sz="1200" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t>                               </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ja-JP" sz="1200">
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ja-JP" sz="1200" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t>             TELL: 0204-3662-777  FAX</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t>:  0204-3662-825                                </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ja-JP" sz="1100">
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
+            <a:t>MASUDA VINYL VIETNAM
+Lô I Đồng vàng, Khu công nghiệp Đình Trám,
+Phường Nếnh, Thị xã Việt Yên, Tỉnh Bắc Giang
+TELL: 0204-3662-777  FAX:  0204-3662-825                                 </a:t>
+          </a:fld>
           <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
             <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
             <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
@@ -2465,16 +1937,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:10" ht="54" customHeight="1">
-      <c r="C1" s="63" t="s">
+      <c r="C1" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="64"/>
-      <c r="E1" s="64"/>
-      <c r="F1" s="64"/>
-      <c r="G1" s="64"/>
-      <c r="H1" s="64"/>
-      <c r="I1" s="64"/>
-      <c r="J1" s="64"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
+      <c r="J1" s="40"/>
     </row>
     <row r="2" spans="2:10" ht="21.75" customHeight="1">
       <c r="C2" s="36"/>
@@ -2542,9 +2014,9 @@
       <c r="J6" s="11"/>
     </row>
     <row r="7" spans="2:10" ht="18.75" customHeight="1">
-      <c r="B7" s="65"/>
-      <c r="C7" s="65"/>
-      <c r="D7" s="65"/>
+      <c r="B7" s="41"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="41"/>
       <c r="E7" s="2"/>
       <c r="F7" s="5"/>
       <c r="G7" s="5"/>
@@ -2562,26 +2034,26 @@
       <c r="I8" s="6"/>
     </row>
     <row r="9" spans="2:10" s="8" customFormat="1" ht="18" customHeight="1">
-      <c r="B9" s="66" t="s">
+      <c r="B9" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="66"/>
-      <c r="D9" s="66"/>
-      <c r="E9" s="66"/>
-      <c r="F9" s="66"/>
-      <c r="G9" s="66"/>
+      <c r="C9" s="42"/>
+      <c r="D9" s="42"/>
+      <c r="E9" s="42"/>
+      <c r="F9" s="42"/>
+      <c r="G9" s="42"/>
       <c r="H9" s="17"/>
       <c r="I9" s="17"/>
     </row>
     <row r="10" spans="2:10" ht="18" customHeight="1">
-      <c r="B10" s="67" t="s">
+      <c r="B10" s="43" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="67"/>
-      <c r="D10" s="67"/>
-      <c r="E10" s="67"/>
-      <c r="F10" s="67"/>
-      <c r="G10" s="67"/>
+      <c r="C10" s="43"/>
+      <c r="D10" s="43"/>
+      <c r="E10" s="43"/>
+      <c r="F10" s="43"/>
+      <c r="G10" s="43"/>
     </row>
     <row r="11" spans="2:10" ht="18" customHeight="1" thickBot="1">
       <c r="D11" s="1"/>
@@ -2593,10 +2065,10 @@
       <c r="B12" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="C12" s="68" t="s">
+      <c r="C12" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="D12" s="69"/>
+      <c r="D12" s="45"/>
       <c r="E12" s="13" t="s">
         <v>6</v>
       </c>
@@ -2609,19 +2081,19 @@
       <c r="H12" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="I12" s="68" t="s">
+      <c r="I12" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="J12" s="70"/>
+      <c r="J12" s="46"/>
     </row>
     <row r="13" spans="2:10" ht="16.5">
       <c r="B13" s="16">
         <v>1</v>
       </c>
-      <c r="C13" s="49" t="s">
+      <c r="C13" s="47" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="49"/>
+      <c r="D13" s="47"/>
       <c r="E13" s="9" t="s">
         <v>13</v>
       </c>
@@ -2632,168 +2104,168 @@
         <v>6600</v>
       </c>
       <c r="H13" s="19"/>
-      <c r="I13" s="53">
+      <c r="I13" s="48">
         <f>IF(NOT(G13*F13=0), G13*F13, "")</f>
         <v>3300000</v>
       </c>
-      <c r="J13" s="54"/>
+      <c r="J13" s="49"/>
     </row>
     <row r="14" spans="2:10" ht="21" customHeight="1">
       <c r="B14" s="16">
         <f>B13+1</f>
         <v>2</v>
       </c>
-      <c r="C14" s="49"/>
-      <c r="D14" s="49"/>
+      <c r="C14" s="47"/>
+      <c r="D14" s="47"/>
       <c r="E14" s="9"/>
       <c r="F14" s="10"/>
       <c r="G14" s="23"/>
       <c r="H14" s="19"/>
-      <c r="I14" s="53" t="str">
+      <c r="I14" s="48" t="str">
         <f>IF(NOT(G14*F14=0), G14*F14, "")</f>
         <v/>
       </c>
-      <c r="J14" s="54"/>
+      <c r="J14" s="49"/>
     </row>
     <row r="15" spans="2:10" ht="20.100000000000001" customHeight="1">
       <c r="B15" s="15">
         <f>B14+1</f>
         <v>3</v>
       </c>
-      <c r="C15" s="52"/>
-      <c r="D15" s="52"/>
+      <c r="C15" s="50"/>
+      <c r="D15" s="50"/>
       <c r="E15" s="9"/>
       <c r="F15" s="10"/>
       <c r="G15" s="22"/>
       <c r="H15" s="19"/>
-      <c r="I15" s="53" t="str">
+      <c r="I15" s="48" t="str">
         <f t="shared" ref="I15:I19" si="0">IF(NOT(G15*F15=0), G15*F15, "")</f>
         <v/>
       </c>
-      <c r="J15" s="54"/>
+      <c r="J15" s="49"/>
     </row>
     <row r="16" spans="2:10" ht="20.100000000000001" customHeight="1">
       <c r="B16" s="15">
         <f>B15+1</f>
         <v>4</v>
       </c>
-      <c r="C16" s="52"/>
-      <c r="D16" s="52"/>
+      <c r="C16" s="50"/>
+      <c r="D16" s="50"/>
       <c r="E16" s="9"/>
       <c r="F16" s="10"/>
       <c r="G16" s="22"/>
       <c r="H16" s="19"/>
-      <c r="I16" s="53" t="str">
+      <c r="I16" s="48" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="J16" s="54"/>
+      <c r="J16" s="49"/>
     </row>
     <row r="17" spans="2:10" ht="20.100000000000001" customHeight="1">
       <c r="B17" s="15">
         <f>B16+1</f>
         <v>5</v>
       </c>
-      <c r="C17" s="52"/>
-      <c r="D17" s="52"/>
+      <c r="C17" s="50"/>
+      <c r="D17" s="50"/>
       <c r="E17" s="9"/>
       <c r="F17" s="10"/>
       <c r="G17" s="22"/>
       <c r="H17" s="19"/>
-      <c r="I17" s="53" t="str">
+      <c r="I17" s="48" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="J17" s="54"/>
+      <c r="J17" s="49"/>
     </row>
     <row r="18" spans="2:10" ht="20.100000000000001" customHeight="1">
       <c r="B18" s="15">
         <f>B17+1</f>
         <v>6</v>
       </c>
-      <c r="C18" s="52"/>
-      <c r="D18" s="52"/>
+      <c r="C18" s="50"/>
+      <c r="D18" s="50"/>
       <c r="E18" s="9"/>
       <c r="F18" s="10"/>
       <c r="G18" s="22"/>
       <c r="H18" s="19"/>
-      <c r="I18" s="53" t="str">
+      <c r="I18" s="48" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="J18" s="54"/>
+      <c r="J18" s="49"/>
     </row>
     <row r="19" spans="2:10" ht="20.100000000000001" customHeight="1">
       <c r="B19" s="15">
         <v>7</v>
       </c>
-      <c r="C19" s="52"/>
-      <c r="D19" s="52"/>
+      <c r="C19" s="50"/>
+      <c r="D19" s="50"/>
       <c r="E19" s="9"/>
       <c r="F19" s="10"/>
       <c r="G19" s="22"/>
       <c r="H19" s="19"/>
-      <c r="I19" s="53" t="str">
+      <c r="I19" s="48" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="J19" s="54"/>
+      <c r="J19" s="49"/>
     </row>
     <row r="20" spans="2:10" ht="30" customHeight="1">
-      <c r="B20" s="55" t="s">
+      <c r="B20" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="C20" s="56"/>
-      <c r="D20" s="56"/>
-      <c r="E20" s="56"/>
-      <c r="F20" s="56"/>
-      <c r="G20" s="56"/>
-      <c r="H20" s="57"/>
-      <c r="I20" s="58">
+      <c r="C20" s="52"/>
+      <c r="D20" s="52"/>
+      <c r="E20" s="52"/>
+      <c r="F20" s="52"/>
+      <c r="G20" s="52"/>
+      <c r="H20" s="53"/>
+      <c r="I20" s="54">
         <f>SUM(I13:J19)</f>
         <v>3300000</v>
       </c>
-      <c r="J20" s="59"/>
+      <c r="J20" s="55"/>
     </row>
     <row r="21" spans="2:10" ht="30" customHeight="1">
-      <c r="B21" s="60" t="s">
+      <c r="B21" s="56" t="s">
         <v>12</v>
       </c>
-      <c r="C21" s="56"/>
-      <c r="D21" s="56"/>
-      <c r="E21" s="56"/>
-      <c r="F21" s="56"/>
-      <c r="G21" s="56"/>
-      <c r="H21" s="57"/>
-      <c r="I21" s="61"/>
-      <c r="J21" s="62"/>
+      <c r="C21" s="52"/>
+      <c r="D21" s="52"/>
+      <c r="E21" s="52"/>
+      <c r="F21" s="52"/>
+      <c r="G21" s="52"/>
+      <c r="H21" s="53"/>
+      <c r="I21" s="57"/>
+      <c r="J21" s="58"/>
     </row>
     <row r="22" spans="2:10" ht="30" customHeight="1" thickBot="1">
-      <c r="B22" s="41" t="s">
+      <c r="B22" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="C22" s="42"/>
-      <c r="D22" s="42"/>
-      <c r="E22" s="42"/>
-      <c r="F22" s="42"/>
-      <c r="G22" s="42"/>
-      <c r="H22" s="43"/>
-      <c r="I22" s="44">
+      <c r="C22" s="60"/>
+      <c r="D22" s="60"/>
+      <c r="E22" s="60"/>
+      <c r="F22" s="60"/>
+      <c r="G22" s="60"/>
+      <c r="H22" s="61"/>
+      <c r="I22" s="62">
         <f>I20+I21</f>
         <v>3300000</v>
       </c>
-      <c r="J22" s="45"/>
+      <c r="J22" s="63"/>
     </row>
     <row r="23" spans="2:10" ht="44.25" customHeight="1" thickBot="1">
-      <c r="B23" s="75"/>
-      <c r="C23" s="76"/>
-      <c r="D23" s="76"/>
-      <c r="E23" s="76"/>
-      <c r="F23" s="76"/>
-      <c r="G23" s="76"/>
-      <c r="H23" s="76"/>
-      <c r="I23" s="76"/>
-      <c r="J23" s="77"/>
+      <c r="B23" s="64"/>
+      <c r="C23" s="65"/>
+      <c r="D23" s="65"/>
+      <c r="E23" s="65"/>
+      <c r="F23" s="65"/>
+      <c r="G23" s="65"/>
+      <c r="H23" s="65"/>
+      <c r="I23" s="65"/>
+      <c r="J23" s="66"/>
     </row>
     <row r="24" spans="2:10" ht="17.25" customHeight="1">
       <c r="D24" s="1"/>
@@ -2802,9 +2274,9 @@
       <c r="G24" s="1"/>
     </row>
     <row r="25" spans="2:10" ht="48" customHeight="1">
-      <c r="B25" s="46"/>
-      <c r="C25" s="46"/>
-      <c r="D25" s="46"/>
+      <c r="B25" s="67"/>
+      <c r="C25" s="67"/>
+      <c r="D25" s="67"/>
       <c r="E25" s="29"/>
       <c r="F25" s="32"/>
       <c r="G25" s="33" t="s">
@@ -2813,37 +2285,37 @@
       <c r="H25" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="I25" s="50" t="s">
+      <c r="I25" s="70" t="s">
         <v>20</v>
       </c>
-      <c r="J25" s="50"/>
+      <c r="J25" s="70"/>
     </row>
     <row r="26" spans="2:10" ht="36.75" customHeight="1">
       <c r="B26" s="30"/>
-      <c r="C26" s="47"/>
-      <c r="D26" s="48"/>
+      <c r="C26" s="68"/>
+      <c r="D26" s="69"/>
       <c r="E26" s="30"/>
-      <c r="F26" s="47"/>
-      <c r="G26" s="49"/>
-      <c r="H26" s="49"/>
-      <c r="I26" s="51"/>
-      <c r="J26" s="51"/>
+      <c r="F26" s="68"/>
+      <c r="G26" s="47"/>
+      <c r="H26" s="47"/>
+      <c r="I26" s="71"/>
+      <c r="J26" s="71"/>
     </row>
     <row r="27" spans="2:10" ht="30" customHeight="1">
       <c r="B27" s="28"/>
-      <c r="C27" s="39"/>
-      <c r="D27" s="39"/>
+      <c r="C27" s="72"/>
+      <c r="D27" s="72"/>
       <c r="E27" s="27"/>
-      <c r="F27" s="47"/>
-      <c r="G27" s="49"/>
-      <c r="H27" s="49"/>
-      <c r="I27" s="51"/>
-      <c r="J27" s="51"/>
+      <c r="F27" s="68"/>
+      <c r="G27" s="47"/>
+      <c r="H27" s="47"/>
+      <c r="I27" s="71"/>
+      <c r="J27" s="71"/>
     </row>
     <row r="28" spans="2:10" ht="30" customHeight="1">
       <c r="B28" s="6"/>
-      <c r="C28" s="39"/>
-      <c r="D28" s="39"/>
+      <c r="C28" s="72"/>
+      <c r="D28" s="72"/>
       <c r="E28" s="27"/>
       <c r="F28" s="20"/>
       <c r="G28" s="20"/>
@@ -2853,8 +2325,8 @@
     </row>
     <row r="29" spans="2:10" ht="30" customHeight="1">
       <c r="B29" s="6"/>
-      <c r="C29" s="39"/>
-      <c r="D29" s="39"/>
+      <c r="C29" s="72"/>
+      <c r="D29" s="72"/>
       <c r="E29" s="27"/>
       <c r="F29" s="20"/>
       <c r="G29" s="20"/>
@@ -2864,8 +2336,8 @@
     </row>
     <row r="30" spans="2:10" ht="30" customHeight="1">
       <c r="B30" s="6"/>
-      <c r="C30" s="39"/>
-      <c r="D30" s="39"/>
+      <c r="C30" s="72"/>
+      <c r="D30" s="72"/>
       <c r="E30" s="27"/>
       <c r="F30" s="20"/>
       <c r="G30" s="20"/>
@@ -2875,8 +2347,8 @@
     </row>
     <row r="31" spans="2:10" ht="30" customHeight="1">
       <c r="B31" s="6"/>
-      <c r="C31" s="39"/>
-      <c r="D31" s="39"/>
+      <c r="C31" s="72"/>
+      <c r="D31" s="72"/>
       <c r="E31" s="27"/>
       <c r="F31" s="20"/>
       <c r="G31" s="20"/>
@@ -2886,8 +2358,8 @@
     </row>
     <row r="32" spans="2:10" ht="30" customHeight="1">
       <c r="B32" s="6"/>
-      <c r="C32" s="39"/>
-      <c r="D32" s="39"/>
+      <c r="C32" s="72"/>
+      <c r="D32" s="72"/>
       <c r="E32" s="27"/>
       <c r="F32" s="21"/>
       <c r="G32" s="21"/>
@@ -2897,8 +2369,8 @@
     </row>
     <row r="33" spans="2:10" ht="30" customHeight="1">
       <c r="B33" s="6"/>
-      <c r="C33" s="40"/>
-      <c r="D33" s="40"/>
+      <c r="C33" s="73"/>
+      <c r="D33" s="73"/>
       <c r="E33" s="28"/>
       <c r="F33" s="21"/>
       <c r="G33" s="21"/>
@@ -2908,8 +2380,8 @@
     </row>
     <row r="34" spans="2:10" ht="30" customHeight="1">
       <c r="B34" s="6"/>
-      <c r="C34" s="40"/>
-      <c r="D34" s="40"/>
+      <c r="C34" s="73"/>
+      <c r="D34" s="73"/>
       <c r="E34" s="28"/>
       <c r="F34" s="21"/>
       <c r="G34" s="21"/>
@@ -2919,8 +2391,8 @@
     </row>
     <row r="35" spans="2:10" ht="30" customHeight="1">
       <c r="B35" s="6"/>
-      <c r="C35" s="40"/>
-      <c r="D35" s="40"/>
+      <c r="C35" s="73"/>
+      <c r="D35" s="73"/>
       <c r="E35" s="28"/>
       <c r="F35" s="21"/>
       <c r="G35" s="21"/>
@@ -2944,30 +2416,15 @@
     <row r="49" ht="20.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="C1:J1"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="B9:G9"/>
-    <mergeCell ref="B10:G10"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="B20:H20"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="B21:H21"/>
-    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="C31:D31"/>
     <mergeCell ref="B22:H22"/>
     <mergeCell ref="I22:J22"/>
     <mergeCell ref="B23:J23"/>
@@ -2978,15 +2435,30 @@
     <mergeCell ref="F26:F27"/>
     <mergeCell ref="I25:J25"/>
     <mergeCell ref="I26:J27"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="B20:H20"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="B21:H21"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="C1:J1"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B9:G9"/>
+    <mergeCell ref="B10:G10"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="I12:J12"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.12" right="0.16" top="0.22" bottom="0.12" header="0.3" footer="0.3"/>
@@ -3017,16 +2489,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:10" ht="54" customHeight="1">
-      <c r="C1" s="63" t="s">
+      <c r="C1" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="64"/>
-      <c r="E1" s="64"/>
-      <c r="F1" s="64"/>
-      <c r="G1" s="64"/>
-      <c r="H1" s="64"/>
-      <c r="I1" s="64"/>
-      <c r="J1" s="64"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
+      <c r="J1" s="40"/>
     </row>
     <row r="2" spans="2:10" ht="21.75" customHeight="1">
       <c r="C2" s="36"/>
@@ -3094,9 +2566,9 @@
       <c r="J6" s="11"/>
     </row>
     <row r="7" spans="2:10" ht="18.75" customHeight="1">
-      <c r="B7" s="65"/>
-      <c r="C7" s="65"/>
-      <c r="D7" s="65"/>
+      <c r="B7" s="41"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="41"/>
       <c r="E7" s="2"/>
       <c r="F7" s="5"/>
       <c r="G7" s="5"/>
@@ -3114,26 +2586,26 @@
       <c r="I8" s="6"/>
     </row>
     <row r="9" spans="2:10" s="8" customFormat="1" ht="18" customHeight="1">
-      <c r="B9" s="66" t="s">
+      <c r="B9" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="66"/>
-      <c r="D9" s="66"/>
-      <c r="E9" s="66"/>
-      <c r="F9" s="66"/>
-      <c r="G9" s="66"/>
+      <c r="C9" s="42"/>
+      <c r="D9" s="42"/>
+      <c r="E9" s="42"/>
+      <c r="F9" s="42"/>
+      <c r="G9" s="42"/>
       <c r="H9" s="17"/>
       <c r="I9" s="17"/>
     </row>
     <row r="10" spans="2:10" ht="18" customHeight="1">
-      <c r="B10" s="67" t="s">
+      <c r="B10" s="43" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="67"/>
-      <c r="D10" s="67"/>
-      <c r="E10" s="67"/>
-      <c r="F10" s="67"/>
-      <c r="G10" s="67"/>
+      <c r="C10" s="43"/>
+      <c r="D10" s="43"/>
+      <c r="E10" s="43"/>
+      <c r="F10" s="43"/>
+      <c r="G10" s="43"/>
     </row>
     <row r="11" spans="2:10" ht="18" customHeight="1" thickBot="1">
       <c r="D11" s="1"/>
@@ -3145,10 +2617,10 @@
       <c r="B12" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="C12" s="68" t="s">
+      <c r="C12" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="D12" s="69"/>
+      <c r="D12" s="45"/>
       <c r="E12" s="13" t="s">
         <v>6</v>
       </c>
@@ -3161,19 +2633,19 @@
       <c r="H12" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="I12" s="68" t="s">
+      <c r="I12" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="J12" s="70"/>
+      <c r="J12" s="46"/>
     </row>
     <row r="13" spans="2:10" ht="16.5">
       <c r="B13" s="16">
         <v>1</v>
       </c>
-      <c r="C13" s="49" t="s">
+      <c r="C13" s="47" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="49"/>
+      <c r="D13" s="47"/>
       <c r="E13" s="9" t="s">
         <v>13</v>
       </c>
@@ -3184,243 +2656,243 @@
         <v>6600</v>
       </c>
       <c r="H13" s="19"/>
-      <c r="I13" s="53">
+      <c r="I13" s="48">
         <f>IF(NOT(G13*F13=0), G13*F13, "")</f>
         <v>3300000</v>
       </c>
-      <c r="J13" s="54"/>
+      <c r="J13" s="49"/>
     </row>
     <row r="14" spans="2:10" ht="21" customHeight="1">
       <c r="B14" s="16">
         <v>2</v>
       </c>
-      <c r="C14" s="49"/>
-      <c r="D14" s="49"/>
+      <c r="C14" s="47"/>
+      <c r="D14" s="47"/>
       <c r="E14" s="9"/>
       <c r="F14" s="10"/>
       <c r="G14" s="23"/>
       <c r="H14" s="19"/>
-      <c r="I14" s="53" t="str">
+      <c r="I14" s="48" t="str">
         <f t="shared" ref="I14:I24" si="0">IF(NOT(G14*F14=0), G14*F14, "")</f>
         <v/>
       </c>
-      <c r="J14" s="54"/>
+      <c r="J14" s="49"/>
     </row>
     <row r="15" spans="2:10" ht="20.100000000000001" customHeight="1">
       <c r="B15" s="16">
         <v>3</v>
       </c>
-      <c r="C15" s="52"/>
-      <c r="D15" s="52"/>
+      <c r="C15" s="50"/>
+      <c r="D15" s="50"/>
       <c r="E15" s="9"/>
       <c r="F15" s="10"/>
       <c r="G15" s="22"/>
       <c r="H15" s="19"/>
-      <c r="I15" s="53" t="str">
+      <c r="I15" s="48" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="J15" s="54"/>
+      <c r="J15" s="49"/>
     </row>
     <row r="16" spans="2:10" ht="20.100000000000001" customHeight="1">
       <c r="B16" s="16">
         <v>4</v>
       </c>
-      <c r="C16" s="52"/>
-      <c r="D16" s="52"/>
+      <c r="C16" s="50"/>
+      <c r="D16" s="50"/>
       <c r="E16" s="9"/>
       <c r="F16" s="10"/>
       <c r="G16" s="22"/>
       <c r="H16" s="19"/>
-      <c r="I16" s="53" t="str">
+      <c r="I16" s="48" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="J16" s="54"/>
+      <c r="J16" s="49"/>
     </row>
     <row r="17" spans="2:10" ht="20.100000000000001" customHeight="1">
       <c r="B17" s="16">
         <v>5</v>
       </c>
-      <c r="C17" s="52"/>
-      <c r="D17" s="52"/>
+      <c r="C17" s="50"/>
+      <c r="D17" s="50"/>
       <c r="E17" s="9"/>
       <c r="F17" s="10"/>
       <c r="G17" s="22"/>
       <c r="H17" s="19"/>
-      <c r="I17" s="53" t="str">
+      <c r="I17" s="48" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="J17" s="54"/>
+      <c r="J17" s="49"/>
     </row>
     <row r="18" spans="2:10" ht="20.100000000000001" customHeight="1">
       <c r="B18" s="16">
         <v>6</v>
       </c>
-      <c r="C18" s="52"/>
-      <c r="D18" s="52"/>
+      <c r="C18" s="50"/>
+      <c r="D18" s="50"/>
       <c r="E18" s="9"/>
       <c r="F18" s="10"/>
       <c r="G18" s="22"/>
       <c r="H18" s="19"/>
-      <c r="I18" s="53" t="str">
+      <c r="I18" s="48" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="J18" s="54"/>
+      <c r="J18" s="49"/>
     </row>
     <row r="19" spans="2:10" ht="20.100000000000001" customHeight="1">
       <c r="B19" s="16">
         <v>7</v>
       </c>
-      <c r="C19" s="52"/>
-      <c r="D19" s="52"/>
+      <c r="C19" s="50"/>
+      <c r="D19" s="50"/>
       <c r="E19" s="9"/>
       <c r="F19" s="10"/>
       <c r="G19" s="22"/>
       <c r="H19" s="19"/>
-      <c r="I19" s="53" t="str">
+      <c r="I19" s="48" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="J19" s="54"/>
+      <c r="J19" s="49"/>
     </row>
     <row r="20" spans="2:10" ht="20.100000000000001" customHeight="1">
       <c r="B20" s="16">
         <v>8</v>
       </c>
-      <c r="C20" s="52"/>
-      <c r="D20" s="52"/>
+      <c r="C20" s="50"/>
+      <c r="D20" s="50"/>
       <c r="E20" s="9"/>
       <c r="F20" s="10"/>
       <c r="G20" s="22"/>
       <c r="H20" s="19"/>
-      <c r="I20" s="53" t="str">
+      <c r="I20" s="48" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="J20" s="54"/>
+      <c r="J20" s="49"/>
     </row>
     <row r="21" spans="2:10" ht="20.100000000000001" customHeight="1">
       <c r="B21" s="16">
         <v>9</v>
       </c>
-      <c r="C21" s="52"/>
-      <c r="D21" s="52"/>
+      <c r="C21" s="50"/>
+      <c r="D21" s="50"/>
       <c r="E21" s="9"/>
       <c r="F21" s="10"/>
       <c r="G21" s="22"/>
       <c r="H21" s="19"/>
-      <c r="I21" s="53" t="str">
+      <c r="I21" s="48" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="J21" s="54"/>
+      <c r="J21" s="49"/>
     </row>
     <row r="22" spans="2:10" ht="20.100000000000001" customHeight="1">
       <c r="B22" s="16">
         <v>10</v>
       </c>
-      <c r="C22" s="52"/>
-      <c r="D22" s="52"/>
+      <c r="C22" s="50"/>
+      <c r="D22" s="50"/>
       <c r="E22" s="9"/>
       <c r="F22" s="10"/>
       <c r="G22" s="22"/>
       <c r="H22" s="19"/>
-      <c r="I22" s="53" t="str">
+      <c r="I22" s="48" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="J22" s="54"/>
+      <c r="J22" s="49"/>
     </row>
     <row r="23" spans="2:10" ht="20.100000000000001" customHeight="1">
       <c r="B23" s="16">
         <v>11</v>
       </c>
-      <c r="C23" s="71"/>
-      <c r="D23" s="72"/>
+      <c r="C23" s="74"/>
+      <c r="D23" s="75"/>
       <c r="E23" s="9"/>
       <c r="F23" s="10"/>
       <c r="G23" s="22"/>
       <c r="H23" s="19"/>
-      <c r="I23" s="53" t="str">
+      <c r="I23" s="48" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="J23" s="54"/>
+      <c r="J23" s="49"/>
     </row>
     <row r="24" spans="2:10" ht="20.100000000000001" customHeight="1">
       <c r="B24" s="16">
         <v>12</v>
       </c>
-      <c r="C24" s="52"/>
-      <c r="D24" s="52"/>
+      <c r="C24" s="50"/>
+      <c r="D24" s="50"/>
       <c r="E24" s="9"/>
       <c r="F24" s="10"/>
       <c r="G24" s="22"/>
       <c r="H24" s="19"/>
-      <c r="I24" s="53" t="str">
+      <c r="I24" s="48" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="J24" s="54"/>
+      <c r="J24" s="49"/>
     </row>
     <row r="25" spans="2:10" ht="30" customHeight="1">
-      <c r="B25" s="55" t="s">
+      <c r="B25" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="C25" s="56"/>
-      <c r="D25" s="56"/>
-      <c r="E25" s="56"/>
-      <c r="F25" s="56"/>
-      <c r="G25" s="56"/>
-      <c r="H25" s="57"/>
-      <c r="I25" s="58">
+      <c r="C25" s="52"/>
+      <c r="D25" s="52"/>
+      <c r="E25" s="52"/>
+      <c r="F25" s="52"/>
+      <c r="G25" s="52"/>
+      <c r="H25" s="53"/>
+      <c r="I25" s="54">
         <f>SUM(I13:J24)</f>
         <v>3300000</v>
       </c>
-      <c r="J25" s="59"/>
+      <c r="J25" s="55"/>
     </row>
     <row r="26" spans="2:10" ht="30" customHeight="1">
-      <c r="B26" s="60" t="s">
+      <c r="B26" s="56" t="s">
         <v>12</v>
       </c>
-      <c r="C26" s="56"/>
-      <c r="D26" s="56"/>
-      <c r="E26" s="56"/>
-      <c r="F26" s="56"/>
-      <c r="G26" s="56"/>
-      <c r="H26" s="57"/>
-      <c r="I26" s="61"/>
-      <c r="J26" s="62"/>
+      <c r="C26" s="52"/>
+      <c r="D26" s="52"/>
+      <c r="E26" s="52"/>
+      <c r="F26" s="52"/>
+      <c r="G26" s="52"/>
+      <c r="H26" s="53"/>
+      <c r="I26" s="57"/>
+      <c r="J26" s="58"/>
     </row>
     <row r="27" spans="2:10" ht="30" customHeight="1" thickBot="1">
-      <c r="B27" s="41" t="s">
+      <c r="B27" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="C27" s="42"/>
-      <c r="D27" s="42"/>
-      <c r="E27" s="42"/>
-      <c r="F27" s="42"/>
-      <c r="G27" s="42"/>
-      <c r="H27" s="43"/>
-      <c r="I27" s="44">
+      <c r="C27" s="60"/>
+      <c r="D27" s="60"/>
+      <c r="E27" s="60"/>
+      <c r="F27" s="60"/>
+      <c r="G27" s="60"/>
+      <c r="H27" s="61"/>
+      <c r="I27" s="62">
         <f>I25+I26</f>
         <v>3300000</v>
       </c>
-      <c r="J27" s="45"/>
+      <c r="J27" s="63"/>
     </row>
     <row r="28" spans="2:10" ht="44.25" customHeight="1" thickBot="1">
-      <c r="B28" s="75"/>
-      <c r="C28" s="76"/>
-      <c r="D28" s="76"/>
-      <c r="E28" s="76"/>
-      <c r="F28" s="76"/>
-      <c r="G28" s="76"/>
-      <c r="H28" s="76"/>
-      <c r="I28" s="76"/>
-      <c r="J28" s="77"/>
+      <c r="B28" s="64"/>
+      <c r="C28" s="65"/>
+      <c r="D28" s="65"/>
+      <c r="E28" s="65"/>
+      <c r="F28" s="65"/>
+      <c r="G28" s="65"/>
+      <c r="H28" s="65"/>
+      <c r="I28" s="65"/>
+      <c r="J28" s="66"/>
     </row>
     <row r="29" spans="2:10" ht="17.25" customHeight="1">
       <c r="D29" s="1"/>
@@ -3429,9 +2901,9 @@
       <c r="G29" s="1"/>
     </row>
     <row r="30" spans="2:10" ht="48" customHeight="1">
-      <c r="B30" s="46"/>
-      <c r="C30" s="46"/>
-      <c r="D30" s="46"/>
+      <c r="B30" s="67"/>
+      <c r="C30" s="67"/>
+      <c r="D30" s="67"/>
       <c r="E30" s="29"/>
       <c r="F30" s="32"/>
       <c r="G30" s="33" t="s">
@@ -3440,37 +2912,37 @@
       <c r="H30" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="I30" s="50" t="s">
+      <c r="I30" s="70" t="s">
         <v>20</v>
       </c>
-      <c r="J30" s="50"/>
+      <c r="J30" s="70"/>
     </row>
     <row r="31" spans="2:10" ht="36.75" customHeight="1">
       <c r="B31" s="30"/>
-      <c r="C31" s="47"/>
-      <c r="D31" s="48"/>
+      <c r="C31" s="68"/>
+      <c r="D31" s="69"/>
       <c r="E31" s="30"/>
-      <c r="F31" s="47"/>
-      <c r="G31" s="49"/>
-      <c r="H31" s="49"/>
-      <c r="I31" s="51"/>
-      <c r="J31" s="51"/>
+      <c r="F31" s="68"/>
+      <c r="G31" s="47"/>
+      <c r="H31" s="47"/>
+      <c r="I31" s="71"/>
+      <c r="J31" s="71"/>
     </row>
     <row r="32" spans="2:10" ht="30" customHeight="1">
       <c r="B32" s="28"/>
-      <c r="C32" s="39"/>
-      <c r="D32" s="39"/>
+      <c r="C32" s="72"/>
+      <c r="D32" s="72"/>
       <c r="E32" s="27"/>
-      <c r="F32" s="47"/>
-      <c r="G32" s="49"/>
-      <c r="H32" s="49"/>
-      <c r="I32" s="51"/>
-      <c r="J32" s="51"/>
+      <c r="F32" s="68"/>
+      <c r="G32" s="47"/>
+      <c r="H32" s="47"/>
+      <c r="I32" s="71"/>
+      <c r="J32" s="71"/>
     </row>
     <row r="33" spans="2:10" ht="30" customHeight="1">
       <c r="B33" s="6"/>
-      <c r="C33" s="39"/>
-      <c r="D33" s="39"/>
+      <c r="C33" s="72"/>
+      <c r="D33" s="72"/>
       <c r="E33" s="27"/>
       <c r="F33" s="20"/>
       <c r="G33" s="20"/>
@@ -3480,8 +2952,8 @@
     </row>
     <row r="34" spans="2:10" ht="30" customHeight="1">
       <c r="B34" s="6"/>
-      <c r="C34" s="39"/>
-      <c r="D34" s="39"/>
+      <c r="C34" s="72"/>
+      <c r="D34" s="72"/>
       <c r="E34" s="27"/>
       <c r="F34" s="20"/>
       <c r="G34" s="20"/>
@@ -3491,8 +2963,8 @@
     </row>
     <row r="35" spans="2:10" ht="30" customHeight="1">
       <c r="B35" s="6"/>
-      <c r="C35" s="39"/>
-      <c r="D35" s="39"/>
+      <c r="C35" s="72"/>
+      <c r="D35" s="72"/>
       <c r="E35" s="27"/>
       <c r="F35" s="20"/>
       <c r="G35" s="20"/>
@@ -3502,8 +2974,8 @@
     </row>
     <row r="36" spans="2:10" ht="30" customHeight="1">
       <c r="B36" s="6"/>
-      <c r="C36" s="39"/>
-      <c r="D36" s="39"/>
+      <c r="C36" s="72"/>
+      <c r="D36" s="72"/>
       <c r="E36" s="27"/>
       <c r="F36" s="20"/>
       <c r="G36" s="20"/>
@@ -3513,8 +2985,8 @@
     </row>
     <row r="37" spans="2:10" ht="30" customHeight="1">
       <c r="B37" s="6"/>
-      <c r="C37" s="39"/>
-      <c r="D37" s="39"/>
+      <c r="C37" s="72"/>
+      <c r="D37" s="72"/>
       <c r="E37" s="27"/>
       <c r="F37" s="21"/>
       <c r="G37" s="21"/>
@@ -3524,8 +2996,8 @@
     </row>
     <row r="38" spans="2:10" ht="30" customHeight="1">
       <c r="B38" s="6"/>
-      <c r="C38" s="40"/>
-      <c r="D38" s="40"/>
+      <c r="C38" s="73"/>
+      <c r="D38" s="73"/>
       <c r="E38" s="28"/>
       <c r="F38" s="21"/>
       <c r="G38" s="21"/>
@@ -3535,8 +3007,8 @@
     </row>
     <row r="39" spans="2:10" ht="30" customHeight="1">
       <c r="B39" s="6"/>
-      <c r="C39" s="40"/>
-      <c r="D39" s="40"/>
+      <c r="C39" s="73"/>
+      <c r="D39" s="73"/>
       <c r="E39" s="28"/>
       <c r="F39" s="21"/>
       <c r="G39" s="21"/>
@@ -3546,8 +3018,8 @@
     </row>
     <row r="40" spans="2:10" ht="30" customHeight="1">
       <c r="B40" s="6"/>
-      <c r="C40" s="40"/>
-      <c r="D40" s="40"/>
+      <c r="C40" s="73"/>
+      <c r="D40" s="73"/>
       <c r="E40" s="28"/>
       <c r="F40" s="21"/>
       <c r="G40" s="21"/>
@@ -3579,43 +3051,6 @@
     </row>
   </sheetData>
   <mergeCells count="53">
-    <mergeCell ref="C1:J1"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="B9:G9"/>
-    <mergeCell ref="B10:G10"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="B25:H25"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="B26:H26"/>
-    <mergeCell ref="I26:J26"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="F31:F32"/>
-    <mergeCell ref="G31:G32"/>
-    <mergeCell ref="H31:H32"/>
-    <mergeCell ref="I31:J32"/>
-    <mergeCell ref="B27:H27"/>
-    <mergeCell ref="I27:J27"/>
-    <mergeCell ref="B28:J28"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="I30:J30"/>
     <mergeCell ref="C38:D38"/>
     <mergeCell ref="C39:D39"/>
     <mergeCell ref="C40:D40"/>
@@ -3632,6 +3067,43 @@
     <mergeCell ref="C35:D35"/>
     <mergeCell ref="C36:D36"/>
     <mergeCell ref="C37:D37"/>
+    <mergeCell ref="B27:H27"/>
+    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="B28:J28"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="F31:F32"/>
+    <mergeCell ref="G31:G32"/>
+    <mergeCell ref="H31:H32"/>
+    <mergeCell ref="I31:J32"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="B25:H25"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="B26:H26"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="C1:J1"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B9:G9"/>
+    <mergeCell ref="B10:G10"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="I12:J12"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.12" right="0.16" top="0.22" bottom="0.12" header="0.3" footer="0.3"/>
@@ -3662,16 +3134,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:10" ht="54" customHeight="1">
-      <c r="C1" s="63" t="s">
+      <c r="C1" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="64"/>
-      <c r="E1" s="64"/>
-      <c r="F1" s="64"/>
-      <c r="G1" s="64"/>
-      <c r="H1" s="64"/>
-      <c r="I1" s="64"/>
-      <c r="J1" s="64"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
+      <c r="J1" s="40"/>
     </row>
     <row r="2" spans="2:10" ht="21.75" customHeight="1">
       <c r="C2" s="36"/>
@@ -3739,9 +3211,9 @@
       <c r="J6" s="11"/>
     </row>
     <row r="7" spans="2:10" ht="18.75" customHeight="1">
-      <c r="B7" s="65"/>
-      <c r="C7" s="65"/>
-      <c r="D7" s="65"/>
+      <c r="B7" s="41"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="41"/>
       <c r="E7" s="2"/>
       <c r="F7" s="5"/>
       <c r="G7" s="5"/>
@@ -3759,26 +3231,26 @@
       <c r="I8" s="6"/>
     </row>
     <row r="9" spans="2:10" s="8" customFormat="1" ht="18" customHeight="1">
-      <c r="B9" s="66" t="s">
+      <c r="B9" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="66"/>
-      <c r="D9" s="66"/>
-      <c r="E9" s="66"/>
-      <c r="F9" s="66"/>
-      <c r="G9" s="66"/>
+      <c r="C9" s="42"/>
+      <c r="D9" s="42"/>
+      <c r="E9" s="42"/>
+      <c r="F9" s="42"/>
+      <c r="G9" s="42"/>
       <c r="H9" s="17"/>
       <c r="I9" s="17"/>
     </row>
     <row r="10" spans="2:10" ht="18" customHeight="1">
-      <c r="B10" s="67" t="s">
+      <c r="B10" s="43" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="67"/>
-      <c r="D10" s="67"/>
-      <c r="E10" s="67"/>
-      <c r="F10" s="67"/>
-      <c r="G10" s="67"/>
+      <c r="C10" s="43"/>
+      <c r="D10" s="43"/>
+      <c r="E10" s="43"/>
+      <c r="F10" s="43"/>
+      <c r="G10" s="43"/>
     </row>
     <row r="11" spans="2:10" ht="18" customHeight="1" thickBot="1">
       <c r="D11" s="1"/>
@@ -3790,10 +3262,10 @@
       <c r="B12" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="C12" s="68" t="s">
+      <c r="C12" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="D12" s="69"/>
+      <c r="D12" s="45"/>
       <c r="E12" s="13" t="s">
         <v>6</v>
       </c>
@@ -3806,19 +3278,19 @@
       <c r="H12" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="I12" s="68" t="s">
+      <c r="I12" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="J12" s="70"/>
+      <c r="J12" s="46"/>
     </row>
     <row r="13" spans="2:10" ht="16.5">
       <c r="B13" s="16">
         <v>1</v>
       </c>
-      <c r="C13" s="49" t="s">
+      <c r="C13" s="47" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="49"/>
+      <c r="D13" s="47"/>
       <c r="E13" s="9" t="s">
         <v>13</v>
       </c>
@@ -3829,323 +3301,323 @@
         <v>6600</v>
       </c>
       <c r="H13" s="19"/>
-      <c r="I13" s="53">
+      <c r="I13" s="48">
         <f>IF(NOT(G13*F13=0), G13*F13, "")</f>
         <v>3300000</v>
       </c>
-      <c r="J13" s="54"/>
+      <c r="J13" s="49"/>
     </row>
     <row r="14" spans="2:10" ht="21" customHeight="1">
       <c r="B14" s="16">
         <v>2</v>
       </c>
-      <c r="C14" s="73"/>
-      <c r="D14" s="74"/>
+      <c r="C14" s="76"/>
+      <c r="D14" s="77"/>
       <c r="E14" s="9"/>
       <c r="F14" s="10"/>
       <c r="G14" s="23"/>
       <c r="H14" s="19"/>
-      <c r="I14" s="53" t="str">
+      <c r="I14" s="48" t="str">
         <f>IF(NOT(G14*F14=0), G14*F14, "")</f>
         <v/>
       </c>
-      <c r="J14" s="54"/>
+      <c r="J14" s="49"/>
     </row>
     <row r="15" spans="2:10" ht="20.100000000000001" customHeight="1">
       <c r="B15" s="16">
         <v>3</v>
       </c>
-      <c r="C15" s="71"/>
-      <c r="D15" s="72"/>
+      <c r="C15" s="74"/>
+      <c r="D15" s="75"/>
       <c r="E15" s="9"/>
       <c r="F15" s="10"/>
       <c r="G15" s="22"/>
       <c r="H15" s="19"/>
-      <c r="I15" s="53" t="str">
+      <c r="I15" s="48" t="str">
         <f t="shared" ref="I15:I21" si="0">IF(NOT(G15*F15=0), G15*F15, "")</f>
         <v/>
       </c>
-      <c r="J15" s="54"/>
+      <c r="J15" s="49"/>
     </row>
     <row r="16" spans="2:10" ht="21" customHeight="1">
       <c r="B16" s="16">
         <v>4</v>
       </c>
-      <c r="C16" s="49"/>
-      <c r="D16" s="49"/>
+      <c r="C16" s="47"/>
+      <c r="D16" s="47"/>
       <c r="E16" s="9"/>
       <c r="F16" s="10"/>
       <c r="G16" s="23"/>
       <c r="H16" s="19"/>
-      <c r="I16" s="53" t="str">
+      <c r="I16" s="48" t="str">
         <f>IF(NOT(G16*F16=0), G16*F16, "")</f>
         <v/>
       </c>
-      <c r="J16" s="54"/>
+      <c r="J16" s="49"/>
     </row>
     <row r="17" spans="2:10" ht="20.100000000000001" customHeight="1">
       <c r="B17" s="16">
         <v>5</v>
       </c>
-      <c r="C17" s="52"/>
-      <c r="D17" s="52"/>
+      <c r="C17" s="50"/>
+      <c r="D17" s="50"/>
       <c r="E17" s="9"/>
       <c r="F17" s="10"/>
       <c r="G17" s="22"/>
       <c r="H17" s="19"/>
-      <c r="I17" s="53" t="str">
+      <c r="I17" s="48" t="str">
         <f t="shared" ref="I17:I19" si="1">IF(NOT(G17*F17=0), G17*F17, "")</f>
         <v/>
       </c>
-      <c r="J17" s="54"/>
+      <c r="J17" s="49"/>
     </row>
     <row r="18" spans="2:10" ht="20.100000000000001" customHeight="1">
       <c r="B18" s="16">
         <v>6</v>
       </c>
-      <c r="C18" s="52"/>
-      <c r="D18" s="52"/>
+      <c r="C18" s="50"/>
+      <c r="D18" s="50"/>
       <c r="E18" s="9"/>
       <c r="F18" s="10"/>
       <c r="G18" s="22"/>
       <c r="H18" s="19"/>
-      <c r="I18" s="53" t="str">
+      <c r="I18" s="48" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J18" s="54"/>
+      <c r="J18" s="49"/>
     </row>
     <row r="19" spans="2:10" ht="20.100000000000001" customHeight="1">
       <c r="B19" s="16">
         <v>7</v>
       </c>
-      <c r="C19" s="52"/>
-      <c r="D19" s="52"/>
+      <c r="C19" s="50"/>
+      <c r="D19" s="50"/>
       <c r="E19" s="9"/>
       <c r="F19" s="10"/>
       <c r="G19" s="22"/>
       <c r="H19" s="19"/>
-      <c r="I19" s="53" t="str">
+      <c r="I19" s="48" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J19" s="54"/>
+      <c r="J19" s="49"/>
     </row>
     <row r="20" spans="2:10" ht="20.100000000000001" customHeight="1">
       <c r="B20" s="16">
         <v>8</v>
       </c>
-      <c r="C20" s="71"/>
-      <c r="D20" s="72"/>
+      <c r="C20" s="74"/>
+      <c r="D20" s="75"/>
       <c r="E20" s="9"/>
       <c r="F20" s="10"/>
       <c r="G20" s="22"/>
       <c r="H20" s="19"/>
-      <c r="I20" s="53" t="str">
+      <c r="I20" s="48" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="J20" s="54"/>
+      <c r="J20" s="49"/>
     </row>
     <row r="21" spans="2:10" ht="20.100000000000001" customHeight="1">
       <c r="B21" s="16">
         <v>9</v>
       </c>
-      <c r="C21" s="71"/>
-      <c r="D21" s="72"/>
+      <c r="C21" s="74"/>
+      <c r="D21" s="75"/>
       <c r="E21" s="9"/>
       <c r="F21" s="10"/>
       <c r="G21" s="22"/>
       <c r="H21" s="19"/>
-      <c r="I21" s="53" t="str">
+      <c r="I21" s="48" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="J21" s="54"/>
+      <c r="J21" s="49"/>
     </row>
     <row r="22" spans="2:10" ht="21" customHeight="1">
       <c r="B22" s="16">
         <v>10</v>
       </c>
-      <c r="C22" s="49"/>
-      <c r="D22" s="49"/>
+      <c r="C22" s="47"/>
+      <c r="D22" s="47"/>
       <c r="E22" s="9"/>
       <c r="F22" s="10"/>
       <c r="G22" s="23"/>
       <c r="H22" s="19"/>
-      <c r="I22" s="53" t="str">
+      <c r="I22" s="48" t="str">
         <f>IF(NOT(G22*F22=0), G22*F22, "")</f>
         <v/>
       </c>
-      <c r="J22" s="54"/>
+      <c r="J22" s="49"/>
     </row>
     <row r="23" spans="2:10" ht="20.100000000000001" customHeight="1">
       <c r="B23" s="16">
         <v>11</v>
       </c>
-      <c r="C23" s="52"/>
-      <c r="D23" s="52"/>
+      <c r="C23" s="50"/>
+      <c r="D23" s="50"/>
       <c r="E23" s="9"/>
       <c r="F23" s="10"/>
       <c r="G23" s="22"/>
       <c r="H23" s="19"/>
-      <c r="I23" s="53" t="str">
+      <c r="I23" s="48" t="str">
         <f t="shared" ref="I23:I29" si="2">IF(NOT(G23*F23=0), G23*F23, "")</f>
         <v/>
       </c>
-      <c r="J23" s="54"/>
+      <c r="J23" s="49"/>
     </row>
     <row r="24" spans="2:10" ht="20.100000000000001" customHeight="1">
       <c r="B24" s="16">
         <v>12</v>
       </c>
-      <c r="C24" s="52"/>
-      <c r="D24" s="52"/>
+      <c r="C24" s="50"/>
+      <c r="D24" s="50"/>
       <c r="E24" s="9"/>
       <c r="F24" s="10"/>
       <c r="G24" s="22"/>
       <c r="H24" s="19"/>
-      <c r="I24" s="53" t="str">
+      <c r="I24" s="48" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J24" s="54"/>
+      <c r="J24" s="49"/>
     </row>
     <row r="25" spans="2:10" ht="20.100000000000001" customHeight="1">
       <c r="B25" s="16">
         <v>13</v>
       </c>
-      <c r="C25" s="52"/>
-      <c r="D25" s="52"/>
+      <c r="C25" s="50"/>
+      <c r="D25" s="50"/>
       <c r="E25" s="9"/>
       <c r="F25" s="10"/>
       <c r="G25" s="22"/>
       <c r="H25" s="19"/>
-      <c r="I25" s="53" t="str">
+      <c r="I25" s="48" t="str">
         <f t="shared" ref="I25:I26" si="3">IF(NOT(G25*F25=0), G25*F25, "")</f>
         <v/>
       </c>
-      <c r="J25" s="54"/>
+      <c r="J25" s="49"/>
     </row>
     <row r="26" spans="2:10" ht="20.100000000000001" customHeight="1">
       <c r="B26" s="16">
         <v>14</v>
       </c>
-      <c r="C26" s="52"/>
-      <c r="D26" s="52"/>
+      <c r="C26" s="50"/>
+      <c r="D26" s="50"/>
       <c r="E26" s="9"/>
       <c r="F26" s="10"/>
       <c r="G26" s="22"/>
       <c r="H26" s="19"/>
-      <c r="I26" s="53" t="str">
+      <c r="I26" s="48" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J26" s="54"/>
+      <c r="J26" s="49"/>
     </row>
     <row r="27" spans="2:10" ht="20.100000000000001" customHeight="1">
       <c r="B27" s="16">
         <v>15</v>
       </c>
-      <c r="C27" s="52"/>
-      <c r="D27" s="52"/>
+      <c r="C27" s="50"/>
+      <c r="D27" s="50"/>
       <c r="E27" s="9"/>
       <c r="F27" s="10"/>
       <c r="G27" s="22"/>
       <c r="H27" s="19"/>
-      <c r="I27" s="53" t="str">
+      <c r="I27" s="48" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J27" s="54"/>
+      <c r="J27" s="49"/>
     </row>
     <row r="28" spans="2:10" ht="20.100000000000001" customHeight="1">
       <c r="B28" s="16">
         <v>16</v>
       </c>
-      <c r="C28" s="52"/>
-      <c r="D28" s="52"/>
+      <c r="C28" s="50"/>
+      <c r="D28" s="50"/>
       <c r="E28" s="9"/>
       <c r="F28" s="10"/>
       <c r="G28" s="22"/>
       <c r="H28" s="19"/>
-      <c r="I28" s="53" t="str">
+      <c r="I28" s="48" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J28" s="54"/>
+      <c r="J28" s="49"/>
     </row>
     <row r="29" spans="2:10" ht="20.100000000000001" customHeight="1">
       <c r="B29" s="16">
         <v>17</v>
       </c>
-      <c r="C29" s="52"/>
-      <c r="D29" s="52"/>
+      <c r="C29" s="50"/>
+      <c r="D29" s="50"/>
       <c r="E29" s="9"/>
       <c r="F29" s="10"/>
       <c r="G29" s="22"/>
       <c r="H29" s="19"/>
-      <c r="I29" s="53" t="str">
+      <c r="I29" s="48" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J29" s="54"/>
+      <c r="J29" s="49"/>
     </row>
     <row r="30" spans="2:10" ht="30" customHeight="1">
-      <c r="B30" s="55" t="s">
+      <c r="B30" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="C30" s="56"/>
-      <c r="D30" s="56"/>
-      <c r="E30" s="56"/>
-      <c r="F30" s="56"/>
-      <c r="G30" s="56"/>
-      <c r="H30" s="57"/>
-      <c r="I30" s="58">
+      <c r="C30" s="52"/>
+      <c r="D30" s="52"/>
+      <c r="E30" s="52"/>
+      <c r="F30" s="52"/>
+      <c r="G30" s="52"/>
+      <c r="H30" s="53"/>
+      <c r="I30" s="54">
         <f>SUM(I13:J29)</f>
         <v>3300000</v>
       </c>
-      <c r="J30" s="59"/>
+      <c r="J30" s="55"/>
     </row>
     <row r="31" spans="2:10" ht="30" customHeight="1">
-      <c r="B31" s="60" t="s">
+      <c r="B31" s="56" t="s">
         <v>12</v>
       </c>
-      <c r="C31" s="56"/>
-      <c r="D31" s="56"/>
-      <c r="E31" s="56"/>
-      <c r="F31" s="56"/>
-      <c r="G31" s="56"/>
-      <c r="H31" s="57"/>
-      <c r="I31" s="61"/>
-      <c r="J31" s="62"/>
+      <c r="C31" s="52"/>
+      <c r="D31" s="52"/>
+      <c r="E31" s="52"/>
+      <c r="F31" s="52"/>
+      <c r="G31" s="52"/>
+      <c r="H31" s="53"/>
+      <c r="I31" s="57"/>
+      <c r="J31" s="58"/>
     </row>
     <row r="32" spans="2:10" ht="30" customHeight="1" thickBot="1">
-      <c r="B32" s="41" t="s">
+      <c r="B32" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="C32" s="42"/>
-      <c r="D32" s="42"/>
-      <c r="E32" s="42"/>
-      <c r="F32" s="42"/>
-      <c r="G32" s="42"/>
-      <c r="H32" s="43"/>
-      <c r="I32" s="44">
+      <c r="C32" s="60"/>
+      <c r="D32" s="60"/>
+      <c r="E32" s="60"/>
+      <c r="F32" s="60"/>
+      <c r="G32" s="60"/>
+      <c r="H32" s="61"/>
+      <c r="I32" s="62">
         <f>I30+I31</f>
         <v>3300000</v>
       </c>
-      <c r="J32" s="45"/>
+      <c r="J32" s="63"/>
     </row>
     <row r="33" spans="2:10" ht="44.25" customHeight="1" thickBot="1">
-      <c r="B33" s="75"/>
-      <c r="C33" s="76"/>
-      <c r="D33" s="76"/>
-      <c r="E33" s="76"/>
-      <c r="F33" s="76"/>
-      <c r="G33" s="76"/>
-      <c r="H33" s="76"/>
-      <c r="I33" s="76"/>
-      <c r="J33" s="77"/>
+      <c r="B33" s="64"/>
+      <c r="C33" s="65"/>
+      <c r="D33" s="65"/>
+      <c r="E33" s="65"/>
+      <c r="F33" s="65"/>
+      <c r="G33" s="65"/>
+      <c r="H33" s="65"/>
+      <c r="I33" s="65"/>
+      <c r="J33" s="66"/>
     </row>
     <row r="34" spans="2:10" ht="17.25" customHeight="1">
       <c r="D34" s="1"/>
@@ -4154,9 +3626,9 @@
       <c r="G34" s="1"/>
     </row>
     <row r="35" spans="2:10" ht="48" customHeight="1">
-      <c r="B35" s="46"/>
-      <c r="C35" s="46"/>
-      <c r="D35" s="46"/>
+      <c r="B35" s="67"/>
+      <c r="C35" s="67"/>
+      <c r="D35" s="67"/>
       <c r="E35" s="29"/>
       <c r="F35" s="32"/>
       <c r="G35" s="33" t="s">
@@ -4165,37 +3637,37 @@
       <c r="H35" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="I35" s="50" t="s">
+      <c r="I35" s="70" t="s">
         <v>20</v>
       </c>
-      <c r="J35" s="50"/>
+      <c r="J35" s="70"/>
     </row>
     <row r="36" spans="2:10" ht="36.75" customHeight="1">
       <c r="B36" s="30"/>
-      <c r="C36" s="47"/>
-      <c r="D36" s="48"/>
+      <c r="C36" s="68"/>
+      <c r="D36" s="69"/>
       <c r="E36" s="30"/>
-      <c r="F36" s="47"/>
-      <c r="G36" s="49"/>
-      <c r="H36" s="49"/>
-      <c r="I36" s="51"/>
-      <c r="J36" s="51"/>
+      <c r="F36" s="68"/>
+      <c r="G36" s="47"/>
+      <c r="H36" s="47"/>
+      <c r="I36" s="71"/>
+      <c r="J36" s="71"/>
     </row>
     <row r="37" spans="2:10" ht="30" customHeight="1">
       <c r="B37" s="28"/>
-      <c r="C37" s="39"/>
-      <c r="D37" s="39"/>
+      <c r="C37" s="72"/>
+      <c r="D37" s="72"/>
       <c r="E37" s="27"/>
-      <c r="F37" s="47"/>
-      <c r="G37" s="49"/>
-      <c r="H37" s="49"/>
-      <c r="I37" s="51"/>
-      <c r="J37" s="51"/>
+      <c r="F37" s="68"/>
+      <c r="G37" s="47"/>
+      <c r="H37" s="47"/>
+      <c r="I37" s="71"/>
+      <c r="J37" s="71"/>
     </row>
     <row r="38" spans="2:10" ht="30" customHeight="1">
       <c r="B38" s="6"/>
-      <c r="C38" s="39"/>
-      <c r="D38" s="39"/>
+      <c r="C38" s="72"/>
+      <c r="D38" s="72"/>
       <c r="E38" s="27"/>
       <c r="F38" s="20"/>
       <c r="G38" s="20"/>
@@ -4205,8 +3677,8 @@
     </row>
     <row r="39" spans="2:10" ht="30" customHeight="1">
       <c r="B39" s="6"/>
-      <c r="C39" s="39"/>
-      <c r="D39" s="39"/>
+      <c r="C39" s="72"/>
+      <c r="D39" s="72"/>
       <c r="E39" s="27"/>
       <c r="F39" s="20"/>
       <c r="G39" s="20"/>
@@ -4216,8 +3688,8 @@
     </row>
     <row r="40" spans="2:10" ht="30" customHeight="1">
       <c r="B40" s="6"/>
-      <c r="C40" s="39"/>
-      <c r="D40" s="39"/>
+      <c r="C40" s="72"/>
+      <c r="D40" s="72"/>
       <c r="E40" s="27"/>
       <c r="F40" s="20"/>
       <c r="G40" s="20"/>
@@ -4227,8 +3699,8 @@
     </row>
     <row r="41" spans="2:10" ht="30" customHeight="1">
       <c r="B41" s="6"/>
-      <c r="C41" s="39"/>
-      <c r="D41" s="39"/>
+      <c r="C41" s="72"/>
+      <c r="D41" s="72"/>
       <c r="E41" s="27"/>
       <c r="F41" s="20"/>
       <c r="G41" s="20"/>
@@ -4238,8 +3710,8 @@
     </row>
     <row r="42" spans="2:10" ht="30" customHeight="1">
       <c r="B42" s="6"/>
-      <c r="C42" s="39"/>
-      <c r="D42" s="39"/>
+      <c r="C42" s="72"/>
+      <c r="D42" s="72"/>
       <c r="E42" s="27"/>
       <c r="F42" s="21"/>
       <c r="G42" s="21"/>
@@ -4249,8 +3721,8 @@
     </row>
     <row r="43" spans="2:10" ht="30" customHeight="1">
       <c r="B43" s="6"/>
-      <c r="C43" s="40"/>
-      <c r="D43" s="40"/>
+      <c r="C43" s="73"/>
+      <c r="D43" s="73"/>
       <c r="E43" s="28"/>
       <c r="F43" s="21"/>
       <c r="G43" s="21"/>
@@ -4260,8 +3732,8 @@
     </row>
     <row r="44" spans="2:10" ht="30" customHeight="1">
       <c r="B44" s="6"/>
-      <c r="C44" s="40"/>
-      <c r="D44" s="40"/>
+      <c r="C44" s="73"/>
+      <c r="D44" s="73"/>
       <c r="E44" s="28"/>
       <c r="F44" s="21"/>
       <c r="G44" s="21"/>
@@ -4271,8 +3743,8 @@
     </row>
     <row r="45" spans="2:10" ht="30" customHeight="1">
       <c r="B45" s="6"/>
-      <c r="C45" s="40"/>
-      <c r="D45" s="40"/>
+      <c r="C45" s="73"/>
+      <c r="D45" s="73"/>
       <c r="E45" s="28"/>
       <c r="F45" s="21"/>
       <c r="G45" s="21"/>
@@ -4304,12 +3776,47 @@
     </row>
   </sheetData>
   <mergeCells count="63">
-    <mergeCell ref="C1:J1"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="B9:G9"/>
-    <mergeCell ref="B10:G10"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="B32:H32"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="B33:J33"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="F36:F37"/>
+    <mergeCell ref="G36:G37"/>
+    <mergeCell ref="H36:H37"/>
+    <mergeCell ref="I36:J37"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="B30:H30"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="B31:H31"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="I26:J26"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="I13:J13"/>
     <mergeCell ref="C22:D22"/>
@@ -4320,57 +3827,41 @@
     <mergeCell ref="C21:D21"/>
     <mergeCell ref="I20:J20"/>
     <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="I27:J27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="I28:J28"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="I26:J26"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="B30:H30"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="B31:H31"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="F36:F37"/>
-    <mergeCell ref="G36:G37"/>
-    <mergeCell ref="H36:H37"/>
-    <mergeCell ref="I36:J37"/>
-    <mergeCell ref="B32:H32"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="B33:J33"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="C44:D44"/>
-    <mergeCell ref="C45:D45"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="C40:D40"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="C42:D42"/>
     <mergeCell ref="I15:J15"/>
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="I14:J14"/>
     <mergeCell ref="C14:D14"/>
     <mergeCell ref="C16:D16"/>
     <mergeCell ref="I16:J16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="C1:J1"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B9:G9"/>
+    <mergeCell ref="B10:G10"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="I12:J12"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.12" right="0.16" top="0.22" bottom="0.12" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32A8B651-F1A4-43A1-AC5A-0B7ED6FBE25D}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="61.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="60">
+      <c r="A1" s="78" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>